--- a/doc/calculations/DDS.xlsx
+++ b/doc/calculations/DDS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciej\Desktop\robaki\Robaki\doc\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09447BF2-4199-4C47-BC7F-10384BF7AF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E375DC0-5DCF-4DB6-8907-46849086C7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5CFEA4A-F1AF-4510-A1CF-A397D6EA8E2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t>A</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Frequency</t>
+  </si>
+  <si>
+    <t>hex</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA44EBB7-137A-41BF-92C4-7A186EE567E4}">
-  <dimension ref="A1:I261"/>
+  <dimension ref="A1:K261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -496,7 +499,7 @@
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -510,13 +513,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2">
         <f>B1/256</f>
         <v>253906.25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>19</v>
       </c>
@@ -530,16 +533,22 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
         <v>16</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>48</v>
       </c>
@@ -553,26 +562,34 @@
         <v>130.81299999999999</v>
       </c>
       <c r="E6">
-        <f>ROUND($B$1 / D6, 0)</f>
+        <f t="shared" ref="E6:E42" si="0">ROUND($B$1 / D6, 0)</f>
         <v>496893</v>
       </c>
       <c r="F6">
         <f>ROUND(POWER(2, $D$1) *D6/($B$2*2), 0)</f>
         <v>1106388</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
+        <f>DEC2HEX(F6, 8)</f>
+        <v>0010E1D4</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <f>SIN(G6 * 2 * PI()/256)</f>
+      <c r="I6">
+        <f>SIN(H6 * 2 * PI()/256)</f>
         <v>0</v>
       </c>
-      <c r="I6">
-        <f>ROUND((H6 + 1) * 127.5, 0)</f>
+      <c r="J6">
+        <f>ROUND((I6 + 1) * 127.5, 0)</f>
         <v>128</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K6" t="str">
+        <f>DEC2HEX(J6, 2)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>49</v>
       </c>
@@ -586,26 +603,34 @@
         <v>138.59100000000001</v>
       </c>
       <c r="E7">
-        <f>ROUND($B$1 / D7, 0)</f>
+        <f t="shared" si="0"/>
         <v>469006</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F42" si="0">ROUND(POWER(2, $D$1) *D7/($B$2*2), 0)</f>
+        <f t="shared" ref="F7:F42" si="1">ROUND(POWER(2, $D$1) *D7/($B$2*2), 0)</f>
         <v>1172172</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="str">
+        <f t="shared" ref="G7:G42" si="2">DEC2HEX(F7, 8)</f>
+        <v>0011E2CC</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="H7">
-        <f t="shared" ref="H7:H70" si="1">SIN(G7 * 2 * PI()/256)</f>
+      <c r="I7">
+        <f t="shared" ref="I7:I70" si="3">SIN(H7 * 2 * PI()/256)</f>
         <v>2.4541228522912288E-2</v>
       </c>
-      <c r="I7">
-        <f t="shared" ref="I7:I70" si="2">ROUND((H7 + 1) * 127.5, 0)</f>
+      <c r="J7">
+        <f t="shared" ref="J7:J70" si="4">ROUND((I7 + 1) * 127.5, 0)</f>
         <v>131</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K70" si="5">DEC2HEX(J7, 2)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>50</v>
       </c>
@@ -619,26 +644,34 @@
         <v>146.83199999999999</v>
       </c>
       <c r="E8">
-        <f>ROUND($B$1 / D8, 0)</f>
+        <f t="shared" si="0"/>
         <v>442683</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1241873</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="str">
+        <f t="shared" si="2"/>
+        <v>0012F311</v>
+      </c>
+      <c r="H8">
         <v>2</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
+      <c r="I8">
+        <f t="shared" si="3"/>
         <v>4.9067674327418015E-2</v>
       </c>
-      <c r="I8">
-        <f t="shared" si="2"/>
+      <c r="J8">
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K8" t="str">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>51</v>
       </c>
@@ -652,26 +685,34 @@
         <v>155.56299999999999</v>
       </c>
       <c r="E9">
-        <f>ROUND($B$1 / D9, 0)</f>
+        <f t="shared" si="0"/>
         <v>417837</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1315718</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="str">
+        <f t="shared" si="2"/>
+        <v>00141386</v>
+      </c>
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
+      <c r="I9">
+        <f t="shared" si="3"/>
         <v>7.3564563599667426E-2</v>
       </c>
-      <c r="I9">
-        <f t="shared" si="2"/>
+      <c r="J9">
+        <f t="shared" si="4"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K9" t="str">
+        <f t="shared" si="5"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>52</v>
       </c>
@@ -685,26 +726,34 @@
         <v>164.81399999999999</v>
       </c>
       <c r="E10">
-        <f>ROUND($B$1 / D10, 0)</f>
+        <f t="shared" si="0"/>
         <v>394384</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1393961</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="str">
+        <f t="shared" si="2"/>
+        <v>00154529</v>
+      </c>
+      <c r="H10">
         <v>4</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
+      <c r="I10">
+        <f t="shared" si="3"/>
         <v>9.8017140329560604E-2</v>
       </c>
-      <c r="I10">
-        <f t="shared" si="2"/>
+      <c r="J10">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K10" t="str">
+        <f t="shared" si="5"/>
+        <v>8C</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>53</v>
       </c>
@@ -718,26 +767,34 @@
         <v>174.614</v>
       </c>
       <c r="E11">
-        <f>ROUND($B$1 / D11, 0)</f>
+        <f t="shared" si="0"/>
         <v>372250</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1476847</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="str">
+        <f t="shared" si="2"/>
+        <v>001688EF</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
+      <c r="I11">
+        <f t="shared" si="3"/>
         <v>0.1224106751992162</v>
       </c>
-      <c r="I11">
-        <f t="shared" si="2"/>
+      <c r="J11">
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K11" t="str">
+        <f t="shared" si="5"/>
+        <v>8F</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>54</v>
       </c>
@@ -751,26 +808,34 @@
         <v>184.99700000000001</v>
       </c>
       <c r="E12">
-        <f>ROUND($B$1 / D12, 0)</f>
+        <f t="shared" si="0"/>
         <v>351357</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1564664</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="str">
+        <f t="shared" si="2"/>
+        <v>0017DFF8</v>
+      </c>
+      <c r="H12">
         <v>6</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="1"/>
+      <c r="I12">
+        <f t="shared" si="3"/>
         <v>0.14673047445536175</v>
       </c>
-      <c r="I12">
-        <f t="shared" si="2"/>
+      <c r="J12">
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K12" t="str">
+        <f t="shared" si="5"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>55</v>
       </c>
@@ -784,26 +849,34 @@
         <v>195.99799999999999</v>
       </c>
       <c r="E13">
-        <f>ROUND($B$1 / D13, 0)</f>
+        <f t="shared" si="0"/>
         <v>331636</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1657708</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="str">
+        <f t="shared" si="2"/>
+        <v>00194B6C</v>
+      </c>
+      <c r="H13">
         <v>7</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="1"/>
+      <c r="I13">
+        <f t="shared" si="3"/>
         <v>0.17096188876030122</v>
       </c>
-      <c r="I13">
-        <f t="shared" si="2"/>
+      <c r="J13">
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K13" t="str">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>56</v>
       </c>
@@ -817,26 +890,34 @@
         <v>207.65199999999999</v>
       </c>
       <c r="E14">
-        <f>ROUND($B$1 / D14, 0)</f>
+        <f t="shared" si="0"/>
         <v>313024</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1756275</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="str">
+        <f t="shared" si="2"/>
+        <v>001ACC73</v>
+      </c>
+      <c r="H14">
         <v>8</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="1"/>
+      <c r="I14">
+        <f t="shared" si="3"/>
         <v>0.19509032201612825</v>
       </c>
-      <c r="I14">
-        <f t="shared" si="2"/>
+      <c r="J14">
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K14" t="str">
+        <f t="shared" si="5"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>57</v>
       </c>
@@ -850,26 +931,34 @@
         <v>220</v>
       </c>
       <c r="E15">
-        <f>ROUND($B$1 / D15, 0)</f>
+        <f t="shared" si="0"/>
         <v>295455</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1860712</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="str">
+        <f t="shared" si="2"/>
+        <v>001C6468</v>
+      </c>
+      <c r="H15">
         <v>9</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
+      <c r="I15">
+        <f t="shared" si="3"/>
         <v>0.2191012401568698</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="2"/>
+      <c r="J15">
+        <f t="shared" si="4"/>
         <v>155</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K15" t="str">
+        <f t="shared" si="5"/>
+        <v>9B</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>58</v>
       </c>
@@ -883,26 +972,34 @@
         <v>233.08199999999999</v>
       </c>
       <c r="E16">
-        <f>ROUND($B$1 / D16, 0)</f>
+        <f t="shared" si="0"/>
         <v>278872</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1971357</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="str">
+        <f t="shared" si="2"/>
+        <v>001E149D</v>
+      </c>
+      <c r="H16">
         <v>10</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
+      <c r="I16">
+        <f t="shared" si="3"/>
         <v>0.24298017990326387</v>
       </c>
-      <c r="I16">
-        <f t="shared" si="2"/>
+      <c r="J16">
+        <f t="shared" si="4"/>
         <v>158</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K16" t="str">
+        <f t="shared" si="5"/>
+        <v>9E</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>59</v>
       </c>
@@ -916,26 +1013,34 @@
         <v>246.94200000000001</v>
       </c>
       <c r="E17">
-        <f>ROUND($B$1 / D17, 0)</f>
+        <f t="shared" si="0"/>
         <v>263220</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2088582</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="str">
+        <f t="shared" si="2"/>
+        <v>001FDE86</v>
+      </c>
+      <c r="H17">
         <v>11</v>
       </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
+      <c r="I17">
+        <f t="shared" si="3"/>
         <v>0.26671275747489837</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="2"/>
+      <c r="J17">
+        <f t="shared" si="4"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K17" t="str">
+        <f t="shared" si="5"/>
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>60</v>
       </c>
@@ -949,26 +1054,34 @@
         <v>261.62599999999998</v>
       </c>
       <c r="E18">
-        <f>ROUND($B$1 / D18, 0)</f>
+        <f t="shared" si="0"/>
         <v>248446</v>
       </c>
       <c r="F18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2212776</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="str">
+        <f t="shared" si="2"/>
+        <v>0021C3A8</v>
+      </c>
+      <c r="H18">
         <v>12</v>
       </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
+      <c r="I18">
+        <f t="shared" si="3"/>
         <v>0.29028467725446233</v>
       </c>
-      <c r="I18">
-        <f t="shared" si="2"/>
+      <c r="J18">
+        <f t="shared" si="4"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K18" t="str">
+        <f t="shared" si="5"/>
+        <v>A5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>61</v>
       </c>
@@ -982,26 +1095,34 @@
         <v>277.18299999999999</v>
       </c>
       <c r="E19">
-        <f>ROUND($B$1 / D19, 0)</f>
+        <f t="shared" si="0"/>
         <v>234502</v>
       </c>
       <c r="F19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2344353</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="str">
+        <f t="shared" si="2"/>
+        <v>0023C5A1</v>
+      </c>
+      <c r="H19">
         <v>13</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
+      <c r="I19">
+        <f t="shared" si="3"/>
         <v>0.31368174039889152</v>
       </c>
-      <c r="I19">
-        <f t="shared" si="2"/>
+      <c r="J19">
+        <f t="shared" si="4"/>
         <v>167</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K19" t="str">
+        <f t="shared" si="5"/>
+        <v>A7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>62</v>
       </c>
@@ -1015,26 +1136,34 @@
         <v>293.66500000000002</v>
       </c>
       <c r="E20">
-        <f>ROUND($B$1 / D20, 0)</f>
+        <f t="shared" si="0"/>
         <v>221341</v>
       </c>
       <c r="F20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2483754</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="str">
+        <f t="shared" si="2"/>
+        <v>0025E62A</v>
+      </c>
+      <c r="H20">
         <v>14</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
+      <c r="I20">
+        <f t="shared" si="3"/>
         <v>0.33688985339222005</v>
       </c>
-      <c r="I20">
-        <f t="shared" si="2"/>
+      <c r="J20">
+        <f t="shared" si="4"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K20" t="str">
+        <f t="shared" si="5"/>
+        <v>AA</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>63</v>
       </c>
@@ -1048,26 +1177,34 @@
         <v>311.12700000000001</v>
       </c>
       <c r="E21">
-        <f>ROUND($B$1 / D21, 0)</f>
+        <f t="shared" si="0"/>
         <v>208918</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2631444</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="str">
+        <f t="shared" si="2"/>
+        <v>00282714</v>
+      </c>
+      <c r="H21">
         <v>15</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
+      <c r="I21">
+        <f t="shared" si="3"/>
         <v>0.35989503653498811</v>
       </c>
-      <c r="I21">
-        <f t="shared" si="2"/>
+      <c r="J21">
+        <f t="shared" si="4"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K21" t="str">
+        <f t="shared" si="5"/>
+        <v>AD</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>64</v>
       </c>
@@ -1081,26 +1218,34 @@
         <v>329.62799999999999</v>
       </c>
       <c r="E22">
-        <f>ROUND($B$1 / D22, 0)</f>
+        <f t="shared" si="0"/>
         <v>197192</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2787922</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="str">
+        <f t="shared" si="2"/>
+        <v>002A8A52</v>
+      </c>
+      <c r="H22">
         <v>16</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
+      <c r="I22">
+        <f t="shared" si="3"/>
         <v>0.38268343236508978</v>
       </c>
-      <c r="I22">
-        <f t="shared" si="2"/>
+      <c r="J22">
+        <f t="shared" si="4"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K22" t="str">
+        <f t="shared" si="5"/>
+        <v>B0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>65</v>
       </c>
@@ -1114,26 +1259,34 @@
         <v>349.22800000000001</v>
       </c>
       <c r="E23">
-        <f>ROUND($B$1 / D23, 0)</f>
+        <f t="shared" si="0"/>
         <v>186125</v>
       </c>
       <c r="F23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2953694</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="str">
+        <f t="shared" si="2"/>
+        <v>002D11DE</v>
+      </c>
+      <c r="H23">
         <v>17</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
+      <c r="I23">
+        <f t="shared" si="3"/>
         <v>0.40524131400498986</v>
       </c>
-      <c r="I23">
-        <f t="shared" si="2"/>
+      <c r="J23">
+        <f t="shared" si="4"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K23" t="str">
+        <f t="shared" si="5"/>
+        <v>B3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>66</v>
       </c>
@@ -1147,26 +1300,34 @@
         <v>369.99400000000003</v>
       </c>
       <c r="E24">
-        <f>ROUND($B$1 / D24, 0)</f>
+        <f t="shared" si="0"/>
         <v>175679</v>
       </c>
       <c r="F24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3129329</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="str">
+        <f t="shared" si="2"/>
+        <v>002FBFF1</v>
+      </c>
+      <c r="H24">
         <v>18</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="1"/>
+      <c r="I24">
+        <f t="shared" si="3"/>
         <v>0.42755509343028208</v>
       </c>
-      <c r="I24">
-        <f t="shared" si="2"/>
+      <c r="J24">
+        <f t="shared" si="4"/>
         <v>182</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K24" t="str">
+        <f t="shared" si="5"/>
+        <v>B6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>67</v>
       </c>
@@ -1180,26 +1341,34 @@
         <v>391.995</v>
       </c>
       <c r="E25">
-        <f>ROUND($B$1 / D25, 0)</f>
+        <f t="shared" si="0"/>
         <v>165818</v>
       </c>
       <c r="F25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3315408</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="str">
+        <f t="shared" si="2"/>
+        <v>003296D0</v>
+      </c>
+      <c r="H25">
         <v>19</v>
       </c>
-      <c r="H25">
-        <f t="shared" si="1"/>
+      <c r="I25">
+        <f t="shared" si="3"/>
         <v>0.44961132965460654</v>
       </c>
-      <c r="I25">
-        <f t="shared" si="2"/>
+      <c r="J25">
+        <f t="shared" si="4"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K25" t="str">
+        <f t="shared" si="5"/>
+        <v>B9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>68</v>
       </c>
@@ -1213,26 +1382,34 @@
         <v>415.30500000000001</v>
       </c>
       <c r="E26">
-        <f>ROUND($B$1 / D26, 0)</f>
+        <f t="shared" si="0"/>
         <v>156511</v>
       </c>
       <c r="F26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3512559</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="str">
+        <f t="shared" si="2"/>
+        <v>003598EF</v>
+      </c>
+      <c r="H26">
         <v>20</v>
       </c>
-      <c r="H26">
-        <f t="shared" si="1"/>
+      <c r="I26">
+        <f t="shared" si="3"/>
         <v>0.47139673682599764</v>
       </c>
-      <c r="I26">
-        <f t="shared" si="2"/>
+      <c r="J26">
+        <f t="shared" si="4"/>
         <v>188</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K26" t="str">
+        <f t="shared" si="5"/>
+        <v>BC</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>69</v>
       </c>
@@ -1246,26 +1423,34 @@
         <v>440</v>
       </c>
       <c r="E27">
-        <f>ROUND($B$1 / D27, 0)</f>
+        <f t="shared" si="0"/>
         <v>147727</v>
       </c>
       <c r="F27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3721424</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="str">
+        <f t="shared" si="2"/>
+        <v>0038C8D0</v>
+      </c>
+      <c r="H27">
         <v>21</v>
       </c>
-      <c r="H27">
-        <f t="shared" si="1"/>
+      <c r="I27">
+        <f t="shared" si="3"/>
         <v>0.49289819222978404</v>
       </c>
-      <c r="I27">
-        <f t="shared" si="2"/>
+      <c r="J27">
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K27" t="str">
+        <f t="shared" si="5"/>
+        <v>BE</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>70</v>
       </c>
@@ -1279,26 +1464,34 @@
         <v>466.16399999999999</v>
       </c>
       <c r="E28">
-        <f>ROUND($B$1 / D28, 0)</f>
+        <f t="shared" si="0"/>
         <v>139436</v>
       </c>
       <c r="F28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3942713</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="str">
+        <f t="shared" si="2"/>
+        <v>003C2939</v>
+      </c>
+      <c r="H28">
         <v>22</v>
       </c>
-      <c r="H28">
-        <f t="shared" si="1"/>
+      <c r="I28">
+        <f t="shared" si="3"/>
         <v>0.51410274419322166</v>
       </c>
-      <c r="I28">
-        <f t="shared" si="2"/>
+      <c r="J28">
+        <f t="shared" si="4"/>
         <v>193</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K28" t="str">
+        <f t="shared" si="5"/>
+        <v>C1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>71</v>
       </c>
@@ -1312,26 +1505,34 @@
         <v>493.88299999999998</v>
       </c>
       <c r="E29">
-        <f>ROUND($B$1 / D29, 0)</f>
+        <f t="shared" si="0"/>
         <v>131610</v>
       </c>
       <c r="F29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4177155</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="str">
+        <f t="shared" si="2"/>
+        <v>003FBD03</v>
+      </c>
+      <c r="H29">
         <v>23</v>
       </c>
-      <c r="H29">
-        <f t="shared" si="1"/>
+      <c r="I29">
+        <f t="shared" si="3"/>
         <v>0.53499761988709715</v>
       </c>
-      <c r="I29">
-        <f t="shared" si="2"/>
+      <c r="J29">
+        <f t="shared" si="4"/>
         <v>196</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K29" t="str">
+        <f t="shared" si="5"/>
+        <v>C4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>72</v>
       </c>
@@ -1345,26 +1546,34 @@
         <v>523.25099999999998</v>
       </c>
       <c r="E30">
-        <f>ROUND($B$1 / D30, 0)</f>
+        <f t="shared" si="0"/>
         <v>124223</v>
       </c>
       <c r="F30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4425543</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="str">
+        <f t="shared" si="2"/>
+        <v>00438747</v>
+      </c>
+      <c r="H30">
         <v>24</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="1"/>
+      <c r="I30">
+        <f t="shared" si="3"/>
         <v>0.55557023301960218</v>
       </c>
-      <c r="I30">
-        <f t="shared" si="2"/>
+      <c r="J30">
+        <f t="shared" si="4"/>
         <v>198</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K30" t="str">
+        <f t="shared" si="5"/>
+        <v>C6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>73</v>
       </c>
@@ -1378,26 +1587,34 @@
         <v>554.36500000000001</v>
       </c>
       <c r="E31">
-        <f>ROUND($B$1 / D31, 0)</f>
+        <f t="shared" si="0"/>
         <v>117251</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4688698</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="str">
+        <f t="shared" si="2"/>
+        <v>00478B3A</v>
+      </c>
+      <c r="H31">
         <v>25</v>
       </c>
-      <c r="H31">
-        <f t="shared" si="1"/>
+      <c r="I31">
+        <f t="shared" si="3"/>
         <v>0.57580819141784534</v>
       </c>
-      <c r="I31">
-        <f t="shared" si="2"/>
+      <c r="J31">
+        <f t="shared" si="4"/>
         <v>201</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K31" t="str">
+        <f t="shared" si="5"/>
+        <v>C9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>74</v>
       </c>
@@ -1411,26 +1628,34 @@
         <v>587.33000000000004</v>
       </c>
       <c r="E32">
-        <f>ROUND($B$1 / D32, 0)</f>
+        <f t="shared" si="0"/>
         <v>110670</v>
       </c>
       <c r="F32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4967509</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="str">
+        <f t="shared" si="2"/>
+        <v>004BCC55</v>
+      </c>
+      <c r="H32">
         <v>26</v>
       </c>
-      <c r="H32">
-        <f t="shared" si="1"/>
+      <c r="I32">
+        <f t="shared" si="3"/>
         <v>0.59569930449243336</v>
       </c>
-      <c r="I32">
-        <f t="shared" si="2"/>
+      <c r="J32">
+        <f t="shared" si="4"/>
         <v>203</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K32" t="str">
+        <f t="shared" si="5"/>
+        <v>CB</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>75</v>
       </c>
@@ -1444,26 +1669,34 @@
         <v>622.25400000000002</v>
       </c>
       <c r="E33">
-        <f>ROUND($B$1 / D33, 0)</f>
+        <f t="shared" si="0"/>
         <v>104459</v>
       </c>
       <c r="F33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5262889</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="str">
+        <f t="shared" si="2"/>
+        <v>00504E29</v>
+      </c>
+      <c r="H33">
         <v>27</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="1"/>
+      <c r="I33">
+        <f t="shared" si="3"/>
         <v>0.61523159058062682</v>
       </c>
-      <c r="I33">
-        <f t="shared" si="2"/>
+      <c r="J33">
+        <f t="shared" si="4"/>
         <v>206</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K33" t="str">
+        <f t="shared" si="5"/>
+        <v>CE</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>76</v>
       </c>
@@ -1477,26 +1710,34 @@
         <v>659.255</v>
       </c>
       <c r="E34">
-        <f>ROUND($B$1 / D34, 0)</f>
+        <f t="shared" si="0"/>
         <v>98596</v>
       </c>
       <c r="F34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5575835</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="str">
+        <f t="shared" si="2"/>
+        <v>0055149B</v>
+      </c>
+      <c r="H34">
         <v>28</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="1"/>
+      <c r="I34">
+        <f t="shared" si="3"/>
         <v>0.63439328416364549</v>
       </c>
-      <c r="I34">
-        <f t="shared" si="2"/>
+      <c r="J34">
+        <f t="shared" si="4"/>
         <v>208</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K34" t="str">
+        <f t="shared" si="5"/>
+        <v>D0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>77</v>
       </c>
@@ -1510,26 +1751,34 @@
         <v>698.45600000000002</v>
       </c>
       <c r="E35">
-        <f>ROUND($B$1 / D35, 0)</f>
+        <f t="shared" si="0"/>
         <v>93062</v>
       </c>
       <c r="F35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5907388</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="str">
+        <f t="shared" si="2"/>
+        <v>005A23BC</v>
+      </c>
+      <c r="H35">
         <v>29</v>
       </c>
-      <c r="H35">
-        <f t="shared" si="1"/>
+      <c r="I35">
+        <f t="shared" si="3"/>
         <v>0.65317284295377676</v>
       </c>
-      <c r="I35">
-        <f t="shared" si="2"/>
+      <c r="J35">
+        <f t="shared" si="4"/>
         <v>211</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K35" t="str">
+        <f t="shared" si="5"/>
+        <v>D3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>78</v>
       </c>
@@ -1543,26 +1792,34 @@
         <v>739.98900000000003</v>
       </c>
       <c r="E36">
-        <f>ROUND($B$1 / D36, 0)</f>
+        <f t="shared" si="0"/>
         <v>87839</v>
       </c>
       <c r="F36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6258665</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="str">
+        <f t="shared" si="2"/>
+        <v>005F7FE9</v>
+      </c>
+      <c r="H36">
         <v>30</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="1"/>
+      <c r="I36">
+        <f t="shared" si="3"/>
         <v>0.67155895484701833</v>
       </c>
-      <c r="I36">
-        <f t="shared" si="2"/>
+      <c r="J36">
+        <f t="shared" si="4"/>
         <v>213</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K36" t="str">
+        <f t="shared" si="5"/>
+        <v>D5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>79</v>
       </c>
@@ -1576,26 +1833,34 @@
         <v>783.99099999999999</v>
       </c>
       <c r="E37">
-        <f>ROUND($B$1 / D37, 0)</f>
+        <f t="shared" si="0"/>
         <v>82909</v>
       </c>
       <c r="F37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6630825</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="str">
+        <f t="shared" si="2"/>
+        <v>00652DA9</v>
+      </c>
+      <c r="H37">
         <v>31</v>
       </c>
-      <c r="H37">
-        <f t="shared" si="1"/>
+      <c r="I37">
+        <f t="shared" si="3"/>
         <v>0.68954054473706683</v>
       </c>
-      <c r="I37">
-        <f t="shared" si="2"/>
+      <c r="J37">
+        <f t="shared" si="4"/>
         <v>215</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K37" t="str">
+        <f t="shared" si="5"/>
+        <v>D7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>80</v>
       </c>
@@ -1609,26 +1874,34 @@
         <v>830.60900000000004</v>
       </c>
       <c r="E38">
-        <f>ROUND($B$1 / D38, 0)</f>
+        <f t="shared" si="0"/>
         <v>78256</v>
       </c>
       <c r="F38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7025110</v>
       </c>
-      <c r="G38">
+      <c r="G38" t="str">
+        <f t="shared" si="2"/>
+        <v>006B31D6</v>
+      </c>
+      <c r="H38">
         <v>32</v>
       </c>
-      <c r="H38">
-        <f t="shared" si="1"/>
+      <c r="I38">
+        <f t="shared" si="3"/>
         <v>0.70710678118654746</v>
       </c>
-      <c r="I38">
-        <f t="shared" si="2"/>
+      <c r="J38">
+        <f t="shared" si="4"/>
         <v>218</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K38" t="str">
+        <f t="shared" si="5"/>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>81</v>
       </c>
@@ -1642,26 +1915,34 @@
         <v>880</v>
       </c>
       <c r="E39">
-        <f>ROUND($B$1 / D39, 0)</f>
+        <f t="shared" si="0"/>
         <v>73864</v>
       </c>
       <c r="F39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7442848</v>
       </c>
-      <c r="G39">
+      <c r="G39" t="str">
+        <f t="shared" si="2"/>
+        <v>007191A0</v>
+      </c>
+      <c r="H39">
         <v>33</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="1"/>
+      <c r="I39">
+        <f t="shared" si="3"/>
         <v>0.72424708295146689</v>
       </c>
-      <c r="I39">
-        <f t="shared" si="2"/>
+      <c r="J39">
+        <f t="shared" si="4"/>
         <v>220</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K39" t="str">
+        <f t="shared" si="5"/>
+        <v>DC</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>82</v>
       </c>
@@ -1675,26 +1956,34 @@
         <v>932.32799999999997</v>
       </c>
       <c r="E40">
-        <f>ROUND($B$1 / D40, 0)</f>
+        <f t="shared" si="0"/>
         <v>69718</v>
       </c>
       <c r="F40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7885427</v>
       </c>
-      <c r="G40">
+      <c r="G40" t="str">
+        <f t="shared" si="2"/>
+        <v>00785273</v>
+      </c>
+      <c r="H40">
         <v>34</v>
       </c>
-      <c r="H40">
-        <f t="shared" si="1"/>
+      <c r="I40">
+        <f t="shared" si="3"/>
         <v>0.74095112535495911</v>
       </c>
-      <c r="I40">
-        <f t="shared" si="2"/>
+      <c r="J40">
+        <f t="shared" si="4"/>
         <v>222</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K40" t="str">
+        <f t="shared" si="5"/>
+        <v>DE</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>83</v>
       </c>
@@ -1708,26 +1997,34 @@
         <v>987.76700000000005</v>
       </c>
       <c r="E41">
-        <f>ROUND($B$1 / D41, 0)</f>
+        <f t="shared" si="0"/>
         <v>65805</v>
       </c>
       <c r="F41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8354318</v>
       </c>
-      <c r="G41">
+      <c r="G41" t="str">
+        <f t="shared" si="2"/>
+        <v>007F7A0E</v>
+      </c>
+      <c r="H41">
         <v>35</v>
       </c>
-      <c r="H41">
-        <f t="shared" si="1"/>
+      <c r="I41">
+        <f t="shared" si="3"/>
         <v>0.75720884650648446</v>
       </c>
-      <c r="I41">
-        <f t="shared" si="2"/>
+      <c r="J41">
+        <f t="shared" si="4"/>
         <v>224</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K41" t="str">
+        <f t="shared" si="5"/>
+        <v>E0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>84</v>
       </c>
@@ -1741,2905 +2038,3789 @@
         <v>1046.5</v>
       </c>
       <c r="E42">
-        <f>ROUND($B$1 / D42, 0)</f>
+        <f t="shared" si="0"/>
         <v>62112</v>
       </c>
       <c r="F42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8851069</v>
       </c>
-      <c r="G42">
+      <c r="G42" t="str">
+        <f t="shared" si="2"/>
+        <v>00870E7D</v>
+      </c>
+      <c r="H42">
         <v>36</v>
       </c>
-      <c r="H42">
-        <f t="shared" si="1"/>
+      <c r="I42">
+        <f t="shared" si="3"/>
         <v>0.77301045336273699</v>
       </c>
-      <c r="I42">
-        <f t="shared" si="2"/>
+      <c r="J42">
+        <f t="shared" si="4"/>
         <v>226</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G43">
+      <c r="K42" t="str">
+        <f t="shared" si="5"/>
+        <v>E2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H43">
         <v>37</v>
       </c>
-      <c r="H43">
-        <f t="shared" si="1"/>
+      <c r="I43">
+        <f t="shared" si="3"/>
         <v>0.78834642762660623</v>
       </c>
-      <c r="I43">
-        <f t="shared" si="2"/>
+      <c r="J43">
+        <f t="shared" si="4"/>
         <v>228</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G44">
+      <c r="K43" t="str">
+        <f t="shared" si="5"/>
+        <v>E4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H44">
         <v>38</v>
       </c>
-      <c r="H44">
-        <f t="shared" si="1"/>
+      <c r="I44">
+        <f t="shared" si="3"/>
         <v>0.80320753148064483</v>
       </c>
-      <c r="I44">
-        <f t="shared" si="2"/>
+      <c r="J44">
+        <f t="shared" si="4"/>
         <v>230</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G45">
+      <c r="K44" t="str">
+        <f t="shared" si="5"/>
+        <v>E6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H45">
         <v>39</v>
       </c>
-      <c r="H45">
-        <f t="shared" si="1"/>
+      <c r="I45">
+        <f t="shared" si="3"/>
         <v>0.81758481315158371</v>
       </c>
-      <c r="I45">
-        <f t="shared" si="2"/>
+      <c r="J45">
+        <f t="shared" si="4"/>
         <v>232</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G46">
+      <c r="K45" t="str">
+        <f t="shared" si="5"/>
+        <v>E8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H46">
         <v>40</v>
       </c>
-      <c r="H46">
-        <f t="shared" si="1"/>
+      <c r="I46">
+        <f t="shared" si="3"/>
         <v>0.83146961230254524</v>
       </c>
-      <c r="I46">
-        <f t="shared" si="2"/>
+      <c r="J46">
+        <f t="shared" si="4"/>
         <v>234</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G47">
+      <c r="K46" t="str">
+        <f t="shared" si="5"/>
+        <v>EA</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H47">
         <v>41</v>
       </c>
-      <c r="H47">
-        <f t="shared" si="1"/>
+      <c r="I47">
+        <f t="shared" si="3"/>
         <v>0.84485356524970701</v>
       </c>
-      <c r="I47">
-        <f t="shared" si="2"/>
+      <c r="J47">
+        <f t="shared" si="4"/>
         <v>235</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G48">
+      <c r="K47" t="str">
+        <f t="shared" si="5"/>
+        <v>EB</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H48">
         <v>42</v>
       </c>
-      <c r="H48">
-        <f t="shared" si="1"/>
+      <c r="I48">
+        <f t="shared" si="3"/>
         <v>0.85772861000027212</v>
       </c>
-      <c r="I48">
-        <f t="shared" si="2"/>
+      <c r="J48">
+        <f t="shared" si="4"/>
         <v>237</v>
       </c>
-    </row>
-    <row r="49" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G49">
+      <c r="K48" t="str">
+        <f t="shared" si="5"/>
+        <v>ED</v>
+      </c>
+    </row>
+    <row r="49" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H49">
         <v>43</v>
       </c>
-      <c r="H49">
-        <f t="shared" si="1"/>
+      <c r="I49">
+        <f t="shared" si="3"/>
         <v>0.87008699110871135</v>
       </c>
-      <c r="I49">
-        <f t="shared" si="2"/>
+      <c r="J49">
+        <f t="shared" si="4"/>
         <v>238</v>
       </c>
-    </row>
-    <row r="50" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G50">
+      <c r="K49" t="str">
+        <f t="shared" si="5"/>
+        <v>EE</v>
+      </c>
+    </row>
+    <row r="50" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H50">
         <v>44</v>
       </c>
-      <c r="H50">
-        <f t="shared" si="1"/>
+      <c r="I50">
+        <f t="shared" si="3"/>
         <v>0.88192126434835494</v>
       </c>
-      <c r="I50">
-        <f t="shared" si="2"/>
+      <c r="J50">
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
-    </row>
-    <row r="51" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G51">
+      <c r="K50" t="str">
+        <f t="shared" si="5"/>
+        <v>F0</v>
+      </c>
+    </row>
+    <row r="51" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H51">
         <v>45</v>
       </c>
-      <c r="H51">
-        <f t="shared" si="1"/>
+      <c r="I51">
+        <f t="shared" si="3"/>
         <v>0.89322430119551532</v>
       </c>
-      <c r="I51">
-        <f t="shared" si="2"/>
+      <c r="J51">
+        <f t="shared" si="4"/>
         <v>241</v>
       </c>
-    </row>
-    <row r="52" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G52">
+      <c r="K51" t="str">
+        <f t="shared" si="5"/>
+        <v>F1</v>
+      </c>
+    </row>
+    <row r="52" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H52">
         <v>46</v>
       </c>
-      <c r="H52">
-        <f t="shared" si="1"/>
+      <c r="I52">
+        <f t="shared" si="3"/>
         <v>0.90398929312344334</v>
       </c>
-      <c r="I52">
-        <f t="shared" si="2"/>
+      <c r="J52">
+        <f t="shared" si="4"/>
         <v>243</v>
       </c>
-    </row>
-    <row r="53" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G53">
+      <c r="K52" t="str">
+        <f t="shared" si="5"/>
+        <v>F3</v>
+      </c>
+    </row>
+    <row r="53" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H53">
         <v>47</v>
       </c>
-      <c r="H53">
-        <f t="shared" si="1"/>
+      <c r="I53">
+        <f t="shared" si="3"/>
         <v>0.91420975570353069</v>
       </c>
-      <c r="I53">
-        <f t="shared" si="2"/>
+      <c r="J53">
+        <f t="shared" si="4"/>
         <v>244</v>
       </c>
-    </row>
-    <row r="54" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G54">
+      <c r="K53" t="str">
+        <f t="shared" si="5"/>
+        <v>F4</v>
+      </c>
+    </row>
+    <row r="54" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H54">
         <v>48</v>
       </c>
-      <c r="H54">
-        <f t="shared" si="1"/>
+      <c r="I54">
+        <f t="shared" si="3"/>
         <v>0.92387953251128674</v>
       </c>
-      <c r="I54">
-        <f t="shared" si="2"/>
+      <c r="J54">
+        <f t="shared" si="4"/>
         <v>245</v>
       </c>
-    </row>
-    <row r="55" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G55">
+      <c r="K54" t="str">
+        <f t="shared" si="5"/>
+        <v>F5</v>
+      </c>
+    </row>
+    <row r="55" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H55">
         <v>49</v>
       </c>
-      <c r="H55">
-        <f t="shared" si="1"/>
+      <c r="I55">
+        <f t="shared" si="3"/>
         <v>0.93299279883473885</v>
       </c>
-      <c r="I55">
-        <f t="shared" si="2"/>
+      <c r="J55">
+        <f t="shared" si="4"/>
         <v>246</v>
       </c>
-    </row>
-    <row r="56" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G56">
+      <c r="K55" t="str">
+        <f t="shared" si="5"/>
+        <v>F6</v>
+      </c>
+    </row>
+    <row r="56" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H56">
         <v>50</v>
       </c>
-      <c r="H56">
-        <f t="shared" si="1"/>
+      <c r="I56">
+        <f t="shared" si="3"/>
         <v>0.94154406518302081</v>
       </c>
-      <c r="I56">
-        <f t="shared" si="2"/>
+      <c r="J56">
+        <f t="shared" si="4"/>
         <v>248</v>
       </c>
-    </row>
-    <row r="57" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G57">
+      <c r="K56" t="str">
+        <f t="shared" si="5"/>
+        <v>F8</v>
+      </c>
+    </row>
+    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H57">
         <v>51</v>
       </c>
-      <c r="H57">
-        <f t="shared" si="1"/>
+      <c r="I57">
+        <f t="shared" si="3"/>
         <v>0.94952818059303667</v>
       </c>
-      <c r="I57">
-        <f t="shared" si="2"/>
+      <c r="J57">
+        <f t="shared" si="4"/>
         <v>249</v>
       </c>
-    </row>
-    <row r="58" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G58">
+      <c r="K57" t="str">
+        <f t="shared" si="5"/>
+        <v>F9</v>
+      </c>
+    </row>
+    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H58">
         <v>52</v>
       </c>
-      <c r="H58">
-        <f t="shared" si="1"/>
+      <c r="I58">
+        <f t="shared" si="3"/>
         <v>0.95694033573220894</v>
       </c>
-      <c r="I58">
-        <f t="shared" si="2"/>
+      <c r="J58">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
-    </row>
-    <row r="59" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G59">
+      <c r="K58" t="str">
+        <f t="shared" si="5"/>
+        <v>FA</v>
+      </c>
+    </row>
+    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H59">
         <v>53</v>
       </c>
-      <c r="H59">
-        <f t="shared" si="1"/>
+      <c r="I59">
+        <f t="shared" si="3"/>
         <v>0.96377606579543984</v>
       </c>
-      <c r="I59">
-        <f t="shared" si="2"/>
+      <c r="J59">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
-    </row>
-    <row r="60" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G60">
+      <c r="K59" t="str">
+        <f t="shared" si="5"/>
+        <v>FA</v>
+      </c>
+    </row>
+    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H60">
         <v>54</v>
       </c>
-      <c r="H60">
-        <f t="shared" si="1"/>
+      <c r="I60">
+        <f t="shared" si="3"/>
         <v>0.97003125319454397</v>
       </c>
-      <c r="I60">
-        <f t="shared" si="2"/>
+      <c r="J60">
+        <f t="shared" si="4"/>
         <v>251</v>
       </c>
-    </row>
-    <row r="61" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G61">
+      <c r="K60" t="str">
+        <f t="shared" si="5"/>
+        <v>FB</v>
+      </c>
+    </row>
+    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H61">
         <v>55</v>
       </c>
-      <c r="H61">
-        <f t="shared" si="1"/>
+      <c r="I61">
+        <f t="shared" si="3"/>
         <v>0.97570213003852857</v>
       </c>
-      <c r="I61">
-        <f t="shared" si="2"/>
+      <c r="J61">
+        <f t="shared" si="4"/>
         <v>252</v>
       </c>
-    </row>
-    <row r="62" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G62">
+      <c r="K61" t="str">
+        <f t="shared" si="5"/>
+        <v>FC</v>
+      </c>
+    </row>
+    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H62">
         <v>56</v>
       </c>
-      <c r="H62">
-        <f t="shared" si="1"/>
+      <c r="I62">
+        <f t="shared" si="3"/>
         <v>0.98078528040323043</v>
       </c>
-      <c r="I62">
-        <f t="shared" si="2"/>
+      <c r="J62">
+        <f t="shared" si="4"/>
         <v>253</v>
       </c>
-    </row>
-    <row r="63" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G63">
+      <c r="K62" t="str">
+        <f t="shared" si="5"/>
+        <v>FD</v>
+      </c>
+    </row>
+    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H63">
         <v>57</v>
       </c>
-      <c r="H63">
-        <f t="shared" si="1"/>
+      <c r="I63">
+        <f t="shared" si="3"/>
         <v>0.98527764238894122</v>
       </c>
-      <c r="I63">
-        <f t="shared" si="2"/>
+      <c r="J63">
+        <f t="shared" si="4"/>
         <v>253</v>
       </c>
-    </row>
-    <row r="64" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G64">
+      <c r="K63" t="str">
+        <f t="shared" si="5"/>
+        <v>FD</v>
+      </c>
+    </row>
+    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H64">
         <v>58</v>
       </c>
-      <c r="H64">
-        <f t="shared" si="1"/>
+      <c r="I64">
+        <f t="shared" si="3"/>
         <v>0.98917650996478101</v>
       </c>
-      <c r="I64">
-        <f t="shared" si="2"/>
+      <c r="J64">
+        <f t="shared" si="4"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K64" t="str">
+        <f t="shared" si="5"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="G65">
+      <c r="H65">
         <v>59</v>
       </c>
-      <c r="H65">
-        <f t="shared" si="1"/>
+      <c r="I65">
+        <f t="shared" si="3"/>
         <v>0.99247953459870997</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="2"/>
+      <c r="J65">
+        <f t="shared" si="4"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K65" t="str">
+        <f t="shared" si="5"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="G66">
+      <c r="H66">
         <v>60</v>
       </c>
-      <c r="H66">
-        <f t="shared" si="1"/>
+      <c r="I66">
+        <f t="shared" si="3"/>
         <v>0.99518472667219682</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="2"/>
+      <c r="J66">
+        <f t="shared" si="4"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K66" t="str">
+        <f t="shared" si="5"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="G67">
+      <c r="H67">
         <v>61</v>
       </c>
-      <c r="H67">
-        <f t="shared" si="1"/>
+      <c r="I67">
+        <f t="shared" si="3"/>
         <v>0.99729045667869021</v>
       </c>
-      <c r="I67">
-        <f t="shared" si="2"/>
+      <c r="J67">
+        <f t="shared" si="4"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K67" t="str">
+        <f t="shared" si="5"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="G68">
+      <c r="H68">
         <v>62</v>
       </c>
-      <c r="H68">
-        <f t="shared" si="1"/>
+      <c r="I68">
+        <f t="shared" si="3"/>
         <v>0.99879545620517241</v>
       </c>
-      <c r="I68">
-        <f t="shared" si="2"/>
+      <c r="J68">
+        <f t="shared" si="4"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K68" t="str">
+        <f t="shared" si="5"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="G69">
+      <c r="H69">
         <v>63</v>
       </c>
-      <c r="H69">
-        <f t="shared" si="1"/>
+      <c r="I69">
+        <f t="shared" si="3"/>
         <v>0.99969881869620425</v>
       </c>
-      <c r="I69">
-        <f t="shared" si="2"/>
+      <c r="J69">
+        <f t="shared" si="4"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K69" t="str">
+        <f t="shared" si="5"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="G70">
+      <c r="H70">
         <v>64</v>
       </c>
-      <c r="H70">
-        <f t="shared" si="1"/>
+      <c r="I70">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I70">
-        <f t="shared" si="2"/>
+      <c r="J70">
+        <f t="shared" si="4"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K70" t="str">
+        <f t="shared" si="5"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="G71">
+      <c r="H71">
         <v>65</v>
       </c>
-      <c r="H71">
-        <f t="shared" ref="H71:H134" si="3">SIN(G71 * 2 * PI()/256)</f>
+      <c r="I71">
+        <f t="shared" ref="I71:I134" si="6">SIN(H71 * 2 * PI()/256)</f>
         <v>0.99969881869620425</v>
       </c>
-      <c r="I71">
-        <f t="shared" ref="I71:I134" si="4">ROUND((H71 + 1) * 127.5, 0)</f>
+      <c r="J71">
+        <f t="shared" ref="J71:J134" si="7">ROUND((I71 + 1) * 127.5, 0)</f>
         <v>255</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K71" t="str">
+        <f t="shared" ref="K71:K134" si="8">DEC2HEX(J71, 2)</f>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="G72">
+      <c r="H72">
         <v>66</v>
       </c>
-      <c r="H72">
-        <f t="shared" si="3"/>
+      <c r="I72">
+        <f t="shared" si="6"/>
         <v>0.99879545620517241</v>
       </c>
-      <c r="I72">
-        <f t="shared" si="4"/>
+      <c r="J72">
+        <f t="shared" si="7"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K72" t="str">
+        <f t="shared" si="8"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="G73">
+      <c r="H73">
         <v>67</v>
       </c>
-      <c r="H73">
-        <f t="shared" si="3"/>
+      <c r="I73">
+        <f t="shared" si="6"/>
         <v>0.99729045667869021</v>
       </c>
-      <c r="I73">
-        <f t="shared" si="4"/>
+      <c r="J73">
+        <f t="shared" si="7"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K73" t="str">
+        <f t="shared" si="8"/>
+        <v>FF</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="G74">
+      <c r="H74">
         <v>68</v>
       </c>
-      <c r="H74">
-        <f t="shared" si="3"/>
+      <c r="I74">
+        <f t="shared" si="6"/>
         <v>0.99518472667219693</v>
       </c>
-      <c r="I74">
-        <f t="shared" si="4"/>
+      <c r="J74">
+        <f t="shared" si="7"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K74" t="str">
+        <f t="shared" si="8"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="G75">
+      <c r="H75">
         <v>69</v>
       </c>
-      <c r="H75">
-        <f t="shared" si="3"/>
+      <c r="I75">
+        <f t="shared" si="6"/>
         <v>0.99247953459870997</v>
       </c>
-      <c r="I75">
-        <f t="shared" si="4"/>
+      <c r="J75">
+        <f t="shared" si="7"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K75" t="str">
+        <f t="shared" si="8"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="G76">
+      <c r="H76">
         <v>70</v>
       </c>
-      <c r="H76">
-        <f t="shared" si="3"/>
+      <c r="I76">
+        <f t="shared" si="6"/>
         <v>0.98917650996478101</v>
       </c>
-      <c r="I76">
-        <f t="shared" si="4"/>
+      <c r="J76">
+        <f t="shared" si="7"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K76" t="str">
+        <f t="shared" si="8"/>
+        <v>FE</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="G77">
+      <c r="H77">
         <v>71</v>
       </c>
-      <c r="H77">
-        <f t="shared" si="3"/>
+      <c r="I77">
+        <f t="shared" si="6"/>
         <v>0.98527764238894122</v>
       </c>
-      <c r="I77">
-        <f t="shared" si="4"/>
+      <c r="J77">
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K77" t="str">
+        <f t="shared" si="8"/>
+        <v>FD</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="G78">
+      <c r="H78">
         <v>72</v>
       </c>
-      <c r="H78">
-        <f t="shared" si="3"/>
+      <c r="I78">
+        <f t="shared" si="6"/>
         <v>0.98078528040323043</v>
       </c>
-      <c r="I78">
-        <f t="shared" si="4"/>
+      <c r="J78">
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K78" t="str">
+        <f t="shared" si="8"/>
+        <v>FD</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="G79">
+      <c r="H79">
         <v>73</v>
       </c>
-      <c r="H79">
-        <f t="shared" si="3"/>
+      <c r="I79">
+        <f t="shared" si="6"/>
         <v>0.97570213003852857</v>
       </c>
-      <c r="I79">
-        <f t="shared" si="4"/>
+      <c r="J79">
+        <f t="shared" si="7"/>
         <v>252</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K79" t="str">
+        <f t="shared" si="8"/>
+        <v>FC</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="G80">
+      <c r="H80">
         <v>74</v>
       </c>
-      <c r="H80">
-        <f t="shared" si="3"/>
+      <c r="I80">
+        <f t="shared" si="6"/>
         <v>0.97003125319454397</v>
       </c>
-      <c r="I80">
-        <f t="shared" si="4"/>
+      <c r="J80">
+        <f t="shared" si="7"/>
         <v>251</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K80" t="str">
+        <f t="shared" si="8"/>
+        <v>FB</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="G81">
+      <c r="H81">
         <v>75</v>
       </c>
-      <c r="H81">
-        <f t="shared" si="3"/>
+      <c r="I81">
+        <f t="shared" si="6"/>
         <v>0.96377606579543984</v>
       </c>
-      <c r="I81">
-        <f t="shared" si="4"/>
+      <c r="J81">
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K81" t="str">
+        <f t="shared" si="8"/>
+        <v>FA</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="G82">
+      <c r="H82">
         <v>76</v>
       </c>
-      <c r="H82">
-        <f t="shared" si="3"/>
+      <c r="I82">
+        <f t="shared" si="6"/>
         <v>0.95694033573220894</v>
       </c>
-      <c r="I82">
-        <f t="shared" si="4"/>
+      <c r="J82">
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K82" t="str">
+        <f t="shared" si="8"/>
+        <v>FA</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="G83">
+      <c r="H83">
         <v>77</v>
       </c>
-      <c r="H83">
-        <f t="shared" si="3"/>
+      <c r="I83">
+        <f t="shared" si="6"/>
         <v>0.94952818059303667</v>
       </c>
-      <c r="I83">
-        <f t="shared" si="4"/>
+      <c r="J83">
+        <f t="shared" si="7"/>
         <v>249</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K83" t="str">
+        <f t="shared" si="8"/>
+        <v>F9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="G84">
+      <c r="H84">
         <v>78</v>
       </c>
-      <c r="H84">
-        <f t="shared" si="3"/>
+      <c r="I84">
+        <f t="shared" si="6"/>
         <v>0.94154406518302081</v>
       </c>
-      <c r="I84">
-        <f t="shared" si="4"/>
+      <c r="J84">
+        <f t="shared" si="7"/>
         <v>248</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K84" t="str">
+        <f t="shared" si="8"/>
+        <v>F8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="G85">
+      <c r="H85">
         <v>79</v>
       </c>
-      <c r="H85">
-        <f t="shared" si="3"/>
+      <c r="I85">
+        <f t="shared" si="6"/>
         <v>0.93299279883473885</v>
       </c>
-      <c r="I85">
-        <f t="shared" si="4"/>
+      <c r="J85">
+        <f t="shared" si="7"/>
         <v>246</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K85" t="str">
+        <f t="shared" si="8"/>
+        <v>F6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="G86">
+      <c r="H86">
         <v>80</v>
       </c>
-      <c r="H86">
-        <f t="shared" si="3"/>
+      <c r="I86">
+        <f t="shared" si="6"/>
         <v>0.92387953251128674</v>
       </c>
-      <c r="I86">
-        <f t="shared" si="4"/>
+      <c r="J86">
+        <f t="shared" si="7"/>
         <v>245</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K86" t="str">
+        <f t="shared" si="8"/>
+        <v>F5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="G87">
+      <c r="H87">
         <v>81</v>
       </c>
-      <c r="H87">
-        <f t="shared" si="3"/>
+      <c r="I87">
+        <f t="shared" si="6"/>
         <v>0.91420975570353069</v>
       </c>
-      <c r="I87">
-        <f t="shared" si="4"/>
+      <c r="J87">
+        <f t="shared" si="7"/>
         <v>244</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K87" t="str">
+        <f t="shared" si="8"/>
+        <v>F4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="G88">
+      <c r="H88">
         <v>82</v>
       </c>
-      <c r="H88">
-        <f t="shared" si="3"/>
+      <c r="I88">
+        <f t="shared" si="6"/>
         <v>0.90398929312344345</v>
       </c>
-      <c r="I88">
-        <f t="shared" si="4"/>
+      <c r="J88">
+        <f t="shared" si="7"/>
         <v>243</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K88" t="str">
+        <f t="shared" si="8"/>
+        <v>F3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="G89">
+      <c r="H89">
         <v>83</v>
       </c>
-      <c r="H89">
-        <f t="shared" si="3"/>
+      <c r="I89">
+        <f t="shared" si="6"/>
         <v>0.89322430119551521</v>
       </c>
-      <c r="I89">
-        <f t="shared" si="4"/>
+      <c r="J89">
+        <f t="shared" si="7"/>
         <v>241</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K89" t="str">
+        <f t="shared" si="8"/>
+        <v>F1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="G90">
+      <c r="H90">
         <v>84</v>
       </c>
-      <c r="H90">
-        <f t="shared" si="3"/>
+      <c r="I90">
+        <f t="shared" si="6"/>
         <v>0.88192126434835505</v>
       </c>
-      <c r="I90">
-        <f t="shared" si="4"/>
+      <c r="J90">
+        <f t="shared" si="7"/>
         <v>240</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K90" t="str">
+        <f t="shared" si="8"/>
+        <v>F0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="G91">
+      <c r="H91">
         <v>85</v>
       </c>
-      <c r="H91">
-        <f t="shared" si="3"/>
+      <c r="I91">
+        <f t="shared" si="6"/>
         <v>0.87008699110871146</v>
       </c>
-      <c r="I91">
-        <f t="shared" si="4"/>
+      <c r="J91">
+        <f t="shared" si="7"/>
         <v>238</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K91" t="str">
+        <f t="shared" si="8"/>
+        <v>EE</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="G92">
+      <c r="H92">
         <v>86</v>
       </c>
-      <c r="H92">
-        <f t="shared" si="3"/>
+      <c r="I92">
+        <f t="shared" si="6"/>
         <v>0.85772861000027212</v>
       </c>
-      <c r="I92">
-        <f t="shared" si="4"/>
+      <c r="J92">
+        <f t="shared" si="7"/>
         <v>237</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K92" t="str">
+        <f t="shared" si="8"/>
+        <v>ED</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="G93">
+      <c r="H93">
         <v>87</v>
       </c>
-      <c r="H93">
-        <f t="shared" si="3"/>
+      <c r="I93">
+        <f t="shared" si="6"/>
         <v>0.84485356524970723</v>
       </c>
-      <c r="I93">
-        <f t="shared" si="4"/>
+      <c r="J93">
+        <f t="shared" si="7"/>
         <v>235</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K93" t="str">
+        <f t="shared" si="8"/>
+        <v>EB</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="G94">
+      <c r="H94">
         <v>88</v>
       </c>
-      <c r="H94">
-        <f t="shared" si="3"/>
+      <c r="I94">
+        <f t="shared" si="6"/>
         <v>0.83146961230254546</v>
       </c>
-      <c r="I94">
-        <f t="shared" si="4"/>
+      <c r="J94">
+        <f t="shared" si="7"/>
         <v>234</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K94" t="str">
+        <f t="shared" si="8"/>
+        <v>EA</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="G95">
+      <c r="H95">
         <v>89</v>
       </c>
-      <c r="H95">
-        <f t="shared" si="3"/>
+      <c r="I95">
+        <f t="shared" si="6"/>
         <v>0.81758481315158371</v>
       </c>
-      <c r="I95">
-        <f t="shared" si="4"/>
+      <c r="J95">
+        <f t="shared" si="7"/>
         <v>232</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K95" t="str">
+        <f t="shared" si="8"/>
+        <v>E8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="G96">
+      <c r="H96">
         <v>90</v>
       </c>
-      <c r="H96">
-        <f t="shared" si="3"/>
+      <c r="I96">
+        <f t="shared" si="6"/>
         <v>0.80320753148064494</v>
       </c>
-      <c r="I96">
-        <f t="shared" si="4"/>
+      <c r="J96">
+        <f t="shared" si="7"/>
         <v>230</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K96" t="str">
+        <f t="shared" si="8"/>
+        <v>E6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="G97">
+      <c r="H97">
         <v>91</v>
       </c>
-      <c r="H97">
-        <f t="shared" si="3"/>
+      <c r="I97">
+        <f t="shared" si="6"/>
         <v>0.78834642762660634</v>
       </c>
-      <c r="I97">
-        <f t="shared" si="4"/>
+      <c r="J97">
+        <f t="shared" si="7"/>
         <v>228</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K97" t="str">
+        <f t="shared" si="8"/>
+        <v>E4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="G98">
+      <c r="H98">
         <v>92</v>
       </c>
-      <c r="H98">
-        <f t="shared" si="3"/>
+      <c r="I98">
+        <f t="shared" si="6"/>
         <v>0.7730104533627371</v>
       </c>
-      <c r="I98">
-        <f t="shared" si="4"/>
+      <c r="J98">
+        <f t="shared" si="7"/>
         <v>226</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K98" t="str">
+        <f t="shared" si="8"/>
+        <v>E2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="G99">
+      <c r="H99">
         <v>93</v>
       </c>
-      <c r="H99">
-        <f t="shared" si="3"/>
+      <c r="I99">
+        <f t="shared" si="6"/>
         <v>0.75720884650648468</v>
       </c>
-      <c r="I99">
-        <f t="shared" si="4"/>
+      <c r="J99">
+        <f t="shared" si="7"/>
         <v>224</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G100">
+      <c r="K99" t="str">
+        <f t="shared" si="8"/>
+        <v>E0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H100">
         <v>94</v>
       </c>
-      <c r="H100">
-        <f t="shared" si="3"/>
+      <c r="I100">
+        <f t="shared" si="6"/>
         <v>0.74095112535495899</v>
       </c>
-      <c r="I100">
-        <f t="shared" si="4"/>
+      <c r="J100">
+        <f t="shared" si="7"/>
         <v>222</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G101">
+      <c r="K100" t="str">
+        <f t="shared" si="8"/>
+        <v>DE</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H101">
         <v>95</v>
       </c>
-      <c r="H101">
-        <f t="shared" si="3"/>
+      <c r="I101">
+        <f t="shared" si="6"/>
         <v>0.72424708295146689</v>
       </c>
-      <c r="I101">
-        <f t="shared" si="4"/>
+      <c r="J101">
+        <f t="shared" si="7"/>
         <v>220</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G102">
+      <c r="K101" t="str">
+        <f t="shared" si="8"/>
+        <v>DC</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H102">
         <v>96</v>
       </c>
-      <c r="H102">
-        <f t="shared" si="3"/>
+      <c r="I102">
+        <f t="shared" si="6"/>
         <v>0.70710678118654757</v>
       </c>
-      <c r="I102">
-        <f t="shared" si="4"/>
+      <c r="J102">
+        <f t="shared" si="7"/>
         <v>218</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G103">
+      <c r="K102" t="str">
+        <f t="shared" si="8"/>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H103">
         <v>97</v>
       </c>
-      <c r="H103">
-        <f t="shared" si="3"/>
+      <c r="I103">
+        <f t="shared" si="6"/>
         <v>0.68954054473706705</v>
       </c>
-      <c r="I103">
-        <f t="shared" si="4"/>
+      <c r="J103">
+        <f t="shared" si="7"/>
         <v>215</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G104">
+      <c r="K103" t="str">
+        <f t="shared" si="8"/>
+        <v>D7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H104">
         <v>98</v>
       </c>
-      <c r="H104">
-        <f t="shared" si="3"/>
+      <c r="I104">
+        <f t="shared" si="6"/>
         <v>0.67155895484701855</v>
       </c>
-      <c r="I104">
-        <f t="shared" si="4"/>
+      <c r="J104">
+        <f t="shared" si="7"/>
         <v>213</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G105">
+      <c r="K104" t="str">
+        <f t="shared" si="8"/>
+        <v>D5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H105">
         <v>99</v>
       </c>
-      <c r="H105">
-        <f t="shared" si="3"/>
+      <c r="I105">
+        <f t="shared" si="6"/>
         <v>0.65317284295377664</v>
       </c>
-      <c r="I105">
-        <f t="shared" si="4"/>
+      <c r="J105">
+        <f t="shared" si="7"/>
         <v>211</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G106">
+      <c r="K105" t="str">
+        <f t="shared" si="8"/>
+        <v>D3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H106">
         <v>100</v>
       </c>
-      <c r="H106">
-        <f t="shared" si="3"/>
+      <c r="I106">
+        <f t="shared" si="6"/>
         <v>0.63439328416364549</v>
       </c>
-      <c r="I106">
-        <f t="shared" si="4"/>
+      <c r="J106">
+        <f t="shared" si="7"/>
         <v>208</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G107">
+      <c r="K106" t="str">
+        <f t="shared" si="8"/>
+        <v>D0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H107">
         <v>101</v>
       </c>
-      <c r="H107">
-        <f t="shared" si="3"/>
+      <c r="I107">
+        <f t="shared" si="6"/>
         <v>0.61523159058062693</v>
       </c>
-      <c r="I107">
-        <f t="shared" si="4"/>
+      <c r="J107">
+        <f t="shared" si="7"/>
         <v>206</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G108">
+      <c r="K107" t="str">
+        <f t="shared" si="8"/>
+        <v>CE</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H108">
         <v>102</v>
       </c>
-      <c r="H108">
-        <f t="shared" si="3"/>
+      <c r="I108">
+        <f t="shared" si="6"/>
         <v>0.59569930449243347</v>
       </c>
-      <c r="I108">
-        <f t="shared" si="4"/>
+      <c r="J108">
+        <f t="shared" si="7"/>
         <v>203</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G109">
+      <c r="K108" t="str">
+        <f t="shared" si="8"/>
+        <v>CB</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H109">
         <v>103</v>
       </c>
-      <c r="H109">
-        <f t="shared" si="3"/>
+      <c r="I109">
+        <f t="shared" si="6"/>
         <v>0.57580819141784545</v>
       </c>
-      <c r="I109">
-        <f t="shared" si="4"/>
+      <c r="J109">
+        <f t="shared" si="7"/>
         <v>201</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G110">
+      <c r="K109" t="str">
+        <f t="shared" si="8"/>
+        <v>C9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H110">
         <v>104</v>
       </c>
-      <c r="H110">
-        <f t="shared" si="3"/>
+      <c r="I110">
+        <f t="shared" si="6"/>
         <v>0.55557023301960218</v>
       </c>
-      <c r="I110">
-        <f t="shared" si="4"/>
+      <c r="J110">
+        <f t="shared" si="7"/>
         <v>198</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G111">
+      <c r="K110" t="str">
+        <f t="shared" si="8"/>
+        <v>C6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H111">
         <v>105</v>
       </c>
-      <c r="H111">
-        <f t="shared" si="3"/>
+      <c r="I111">
+        <f t="shared" si="6"/>
         <v>0.53499761988709715</v>
       </c>
-      <c r="I111">
-        <f t="shared" si="4"/>
+      <c r="J111">
+        <f t="shared" si="7"/>
         <v>196</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G112">
+      <c r="K111" t="str">
+        <f t="shared" si="8"/>
+        <v>C4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H112">
         <v>106</v>
       </c>
-      <c r="H112">
-        <f t="shared" si="3"/>
+      <c r="I112">
+        <f t="shared" si="6"/>
         <v>0.51410274419322177</v>
       </c>
-      <c r="I112">
-        <f t="shared" si="4"/>
+      <c r="J112">
+        <f t="shared" si="7"/>
         <v>193</v>
       </c>
-    </row>
-    <row r="113" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G113">
+      <c r="K112" t="str">
+        <f t="shared" si="8"/>
+        <v>C1</v>
+      </c>
+    </row>
+    <row r="113" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H113">
         <v>107</v>
       </c>
-      <c r="H113">
-        <f t="shared" si="3"/>
+      <c r="I113">
+        <f t="shared" si="6"/>
         <v>0.49289819222978415</v>
       </c>
-      <c r="I113">
-        <f t="shared" si="4"/>
+      <c r="J113">
+        <f t="shared" si="7"/>
         <v>190</v>
       </c>
-    </row>
-    <row r="114" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G114">
+      <c r="K113" t="str">
+        <f t="shared" si="8"/>
+        <v>BE</v>
+      </c>
+    </row>
+    <row r="114" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H114">
         <v>108</v>
       </c>
-      <c r="H114">
-        <f t="shared" si="3"/>
+      <c r="I114">
+        <f t="shared" si="6"/>
         <v>0.47139673682599786</v>
       </c>
-      <c r="I114">
-        <f t="shared" si="4"/>
+      <c r="J114">
+        <f t="shared" si="7"/>
         <v>188</v>
       </c>
-    </row>
-    <row r="115" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G115">
+      <c r="K114" t="str">
+        <f t="shared" si="8"/>
+        <v>BC</v>
+      </c>
+    </row>
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H115">
         <v>109</v>
       </c>
-      <c r="H115">
-        <f t="shared" si="3"/>
+      <c r="I115">
+        <f t="shared" si="6"/>
         <v>0.44961132965460687</v>
       </c>
-      <c r="I115">
-        <f t="shared" si="4"/>
+      <c r="J115">
+        <f t="shared" si="7"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="116" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G116">
+      <c r="K115" t="str">
+        <f t="shared" si="8"/>
+        <v>B9</v>
+      </c>
+    </row>
+    <row r="116" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H116">
         <v>110</v>
       </c>
-      <c r="H116">
-        <f t="shared" si="3"/>
+      <c r="I116">
+        <f t="shared" si="6"/>
         <v>0.42755509343028203</v>
       </c>
-      <c r="I116">
-        <f t="shared" si="4"/>
+      <c r="J116">
+        <f t="shared" si="7"/>
         <v>182</v>
       </c>
-    </row>
-    <row r="117" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G117">
+      <c r="K116" t="str">
+        <f t="shared" si="8"/>
+        <v>B6</v>
+      </c>
+    </row>
+    <row r="117" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H117">
         <v>111</v>
       </c>
-      <c r="H117">
-        <f t="shared" si="3"/>
+      <c r="I117">
+        <f t="shared" si="6"/>
         <v>0.40524131400498992</v>
       </c>
-      <c r="I117">
-        <f t="shared" si="4"/>
+      <c r="J117">
+        <f t="shared" si="7"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="118" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G118">
+      <c r="K117" t="str">
+        <f t="shared" si="8"/>
+        <v>B3</v>
+      </c>
+    </row>
+    <row r="118" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H118">
         <v>112</v>
       </c>
-      <c r="H118">
-        <f t="shared" si="3"/>
+      <c r="I118">
+        <f t="shared" si="6"/>
         <v>0.38268343236508989</v>
       </c>
-      <c r="I118">
-        <f t="shared" si="4"/>
+      <c r="J118">
+        <f t="shared" si="7"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="119" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G119">
+      <c r="K118" t="str">
+        <f t="shared" si="8"/>
+        <v>B0</v>
+      </c>
+    </row>
+    <row r="119" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H119">
         <v>113</v>
       </c>
-      <c r="H119">
-        <f t="shared" si="3"/>
+      <c r="I119">
+        <f t="shared" si="6"/>
         <v>0.35989503653498833</v>
       </c>
-      <c r="I119">
-        <f t="shared" si="4"/>
+      <c r="J119">
+        <f t="shared" si="7"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="120" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G120">
+      <c r="K119" t="str">
+        <f t="shared" si="8"/>
+        <v>AD</v>
+      </c>
+    </row>
+    <row r="120" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H120">
         <v>114</v>
       </c>
-      <c r="H120">
-        <f t="shared" si="3"/>
+      <c r="I120">
+        <f t="shared" si="6"/>
         <v>0.33688985339222033</v>
       </c>
-      <c r="I120">
-        <f t="shared" si="4"/>
+      <c r="J120">
+        <f t="shared" si="7"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="121" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G121">
+      <c r="K120" t="str">
+        <f t="shared" si="8"/>
+        <v>AA</v>
+      </c>
+    </row>
+    <row r="121" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H121">
         <v>115</v>
       </c>
-      <c r="H121">
-        <f t="shared" si="3"/>
+      <c r="I121">
+        <f t="shared" si="6"/>
         <v>0.31368174039889141</v>
       </c>
-      <c r="I121">
-        <f t="shared" si="4"/>
+      <c r="J121">
+        <f t="shared" si="7"/>
         <v>167</v>
       </c>
-    </row>
-    <row r="122" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G122">
+      <c r="K121" t="str">
+        <f t="shared" si="8"/>
+        <v>A7</v>
+      </c>
+    </row>
+    <row r="122" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H122">
         <v>116</v>
       </c>
-      <c r="H122">
-        <f t="shared" si="3"/>
+      <c r="I122">
+        <f t="shared" si="6"/>
         <v>0.29028467725446239</v>
       </c>
-      <c r="I122">
-        <f t="shared" si="4"/>
+      <c r="J122">
+        <f t="shared" si="7"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="123" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G123">
+      <c r="K122" t="str">
+        <f t="shared" si="8"/>
+        <v>A5</v>
+      </c>
+    </row>
+    <row r="123" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H123">
         <v>117</v>
       </c>
-      <c r="H123">
-        <f t="shared" si="3"/>
+      <c r="I123">
+        <f t="shared" si="6"/>
         <v>0.26671275747489848</v>
       </c>
-      <c r="I123">
-        <f t="shared" si="4"/>
+      <c r="J123">
+        <f t="shared" si="7"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="124" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G124">
+      <c r="K123" t="str">
+        <f t="shared" si="8"/>
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="124" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H124">
         <v>118</v>
       </c>
-      <c r="H124">
-        <f t="shared" si="3"/>
+      <c r="I124">
+        <f t="shared" si="6"/>
         <v>0.24298017990326407</v>
       </c>
-      <c r="I124">
-        <f t="shared" si="4"/>
+      <c r="J124">
+        <f t="shared" si="7"/>
         <v>158</v>
       </c>
-    </row>
-    <row r="125" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G125">
+      <c r="K124" t="str">
+        <f t="shared" si="8"/>
+        <v>9E</v>
+      </c>
+    </row>
+    <row r="125" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H125">
         <v>119</v>
       </c>
-      <c r="H125">
-        <f t="shared" si="3"/>
+      <c r="I125">
+        <f t="shared" si="6"/>
         <v>0.21910124015687005</v>
       </c>
-      <c r="I125">
-        <f t="shared" si="4"/>
+      <c r="J125">
+        <f t="shared" si="7"/>
         <v>155</v>
       </c>
-    </row>
-    <row r="126" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G126">
+      <c r="K125" t="str">
+        <f t="shared" si="8"/>
+        <v>9B</v>
+      </c>
+    </row>
+    <row r="126" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H126">
         <v>120</v>
       </c>
-      <c r="H126">
-        <f t="shared" si="3"/>
+      <c r="I126">
+        <f t="shared" si="6"/>
         <v>0.19509032201612861</v>
       </c>
-      <c r="I126">
-        <f t="shared" si="4"/>
+      <c r="J126">
+        <f t="shared" si="7"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="127" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G127">
+      <c r="K126" t="str">
+        <f t="shared" si="8"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H127">
         <v>121</v>
       </c>
-      <c r="H127">
-        <f t="shared" si="3"/>
+      <c r="I127">
+        <f t="shared" si="6"/>
         <v>0.17096188876030122</v>
       </c>
-      <c r="I127">
-        <f t="shared" si="4"/>
+      <c r="J127">
+        <f t="shared" si="7"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="128" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G128">
+      <c r="K127" t="str">
+        <f t="shared" si="8"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H128">
         <v>122</v>
       </c>
-      <c r="H128">
-        <f t="shared" si="3"/>
+      <c r="I128">
+        <f t="shared" si="6"/>
         <v>0.1467304744553618</v>
       </c>
-      <c r="I128">
-        <f t="shared" si="4"/>
+      <c r="J128">
+        <f t="shared" si="7"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G129">
+      <c r="K128" t="str">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="129" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H129">
         <v>123</v>
       </c>
-      <c r="H129">
-        <f t="shared" si="3"/>
+      <c r="I129">
+        <f t="shared" si="6"/>
         <v>0.12241067519921635</v>
       </c>
-      <c r="I129">
-        <f t="shared" si="4"/>
+      <c r="J129">
+        <f t="shared" si="7"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G130">
+      <c r="K129" t="str">
+        <f t="shared" si="8"/>
+        <v>8F</v>
+      </c>
+    </row>
+    <row r="130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H130">
         <v>124</v>
       </c>
-      <c r="H130">
-        <f t="shared" si="3"/>
+      <c r="I130">
+        <f t="shared" si="6"/>
         <v>9.8017140329560826E-2</v>
       </c>
-      <c r="I130">
-        <f t="shared" si="4"/>
+      <c r="J130">
+        <f t="shared" si="7"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G131">
+      <c r="K130" t="str">
+        <f t="shared" si="8"/>
+        <v>8C</v>
+      </c>
+    </row>
+    <row r="131" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H131">
         <v>125</v>
       </c>
-      <c r="H131">
-        <f t="shared" si="3"/>
+      <c r="I131">
+        <f t="shared" si="6"/>
         <v>7.3564563599667732E-2</v>
       </c>
-      <c r="I131">
-        <f t="shared" si="4"/>
+      <c r="J131">
+        <f t="shared" si="7"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G132">
+      <c r="K131" t="str">
+        <f t="shared" si="8"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="132" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H132">
         <v>126</v>
       </c>
-      <c r="H132">
-        <f t="shared" si="3"/>
+      <c r="I132">
+        <f t="shared" si="6"/>
         <v>4.9067674327417966E-2</v>
       </c>
-      <c r="I132">
-        <f t="shared" si="4"/>
+      <c r="J132">
+        <f t="shared" si="7"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G133">
+      <c r="K132" t="str">
+        <f t="shared" si="8"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="133" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H133">
         <v>127</v>
       </c>
-      <c r="H133">
-        <f t="shared" si="3"/>
+      <c r="I133">
+        <f t="shared" si="6"/>
         <v>2.4541228522912326E-2</v>
       </c>
-      <c r="I133">
-        <f t="shared" si="4"/>
+      <c r="J133">
+        <f t="shared" si="7"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G134">
+      <c r="K133" t="str">
+        <f t="shared" si="8"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="134" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H134">
         <v>128</v>
       </c>
-      <c r="H134">
-        <f t="shared" si="3"/>
+      <c r="I134">
+        <f t="shared" si="6"/>
         <v>1.22514845490862E-16</v>
       </c>
-      <c r="I134">
-        <f t="shared" si="4"/>
+      <c r="J134">
+        <f t="shared" si="7"/>
         <v>128</v>
       </c>
-    </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G135">
+      <c r="K134" t="str">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H135">
         <v>129</v>
       </c>
-      <c r="H135">
-        <f t="shared" ref="H135:H198" si="5">SIN(G135 * 2 * PI()/256)</f>
+      <c r="I135">
+        <f t="shared" ref="I135:I198" si="9">SIN(H135 * 2 * PI()/256)</f>
         <v>-2.454122852291208E-2</v>
       </c>
-      <c r="I135">
-        <f t="shared" ref="I135:I198" si="6">ROUND((H135 + 1) * 127.5, 0)</f>
+      <c r="J135">
+        <f t="shared" ref="J135:J198" si="10">ROUND((I135 + 1) * 127.5, 0)</f>
         <v>124</v>
       </c>
-    </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G136">
+      <c r="K135" t="str">
+        <f t="shared" ref="K135:K198" si="11">DEC2HEX(J135, 2)</f>
+        <v>7C</v>
+      </c>
+    </row>
+    <row r="136" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H136">
         <v>130</v>
       </c>
-      <c r="H136">
-        <f t="shared" si="5"/>
+      <c r="I136">
+        <f t="shared" si="9"/>
         <v>-4.9067674327417724E-2</v>
       </c>
-      <c r="I136">
-        <f t="shared" si="6"/>
+      <c r="J136">
+        <f t="shared" si="10"/>
         <v>121</v>
       </c>
-    </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G137">
+      <c r="K136" t="str">
+        <f t="shared" si="11"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="137" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H137">
         <v>131</v>
       </c>
-      <c r="H137">
-        <f t="shared" si="5"/>
+      <c r="I137">
+        <f t="shared" si="9"/>
         <v>-7.3564563599667496E-2</v>
       </c>
-      <c r="I137">
-        <f t="shared" si="6"/>
+      <c r="J137">
+        <f t="shared" si="10"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G138">
+      <c r="K137" t="str">
+        <f t="shared" si="11"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="138" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H138">
         <v>132</v>
       </c>
-      <c r="H138">
-        <f t="shared" si="5"/>
+      <c r="I138">
+        <f t="shared" si="9"/>
         <v>-9.801714032956059E-2</v>
       </c>
-      <c r="I138">
-        <f t="shared" si="6"/>
+      <c r="J138">
+        <f t="shared" si="10"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G139">
+      <c r="K138" t="str">
+        <f t="shared" si="11"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H139">
         <v>133</v>
       </c>
-      <c r="H139">
-        <f t="shared" si="5"/>
+      <c r="I139">
+        <f t="shared" si="9"/>
         <v>-0.1224106751992161</v>
       </c>
-      <c r="I139">
-        <f t="shared" si="6"/>
+      <c r="J139">
+        <f t="shared" si="10"/>
         <v>112</v>
       </c>
-    </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G140">
+      <c r="K139" t="str">
+        <f t="shared" si="11"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="140" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H140">
         <v>134</v>
       </c>
-      <c r="H140">
-        <f t="shared" si="5"/>
+      <c r="I140">
+        <f t="shared" si="9"/>
         <v>-0.14673047445536158</v>
       </c>
-      <c r="I140">
-        <f t="shared" si="6"/>
+      <c r="J140">
+        <f t="shared" si="10"/>
         <v>109</v>
       </c>
-    </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G141">
+      <c r="K140" t="str">
+        <f t="shared" si="11"/>
+        <v>6D</v>
+      </c>
+    </row>
+    <row r="141" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H141">
         <v>135</v>
       </c>
-      <c r="H141">
-        <f t="shared" si="5"/>
+      <c r="I141">
+        <f t="shared" si="9"/>
         <v>-0.17096188876030097</v>
       </c>
-      <c r="I141">
-        <f t="shared" si="6"/>
+      <c r="J141">
+        <f t="shared" si="10"/>
         <v>106</v>
       </c>
-    </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G142">
+      <c r="K141" t="str">
+        <f t="shared" si="11"/>
+        <v>6A</v>
+      </c>
+    </row>
+    <row r="142" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H142">
         <v>136</v>
       </c>
-      <c r="H142">
-        <f t="shared" si="5"/>
+      <c r="I142">
+        <f t="shared" si="9"/>
         <v>-0.19509032201612836</v>
       </c>
-      <c r="I142">
-        <f t="shared" si="6"/>
+      <c r="J142">
+        <f t="shared" si="10"/>
         <v>103</v>
       </c>
-    </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G143">
+      <c r="K142" t="str">
+        <f t="shared" si="11"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="143" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H143">
         <v>137</v>
       </c>
-      <c r="H143">
-        <f t="shared" si="5"/>
+      <c r="I143">
+        <f t="shared" si="9"/>
         <v>-0.2191012401568698</v>
       </c>
-      <c r="I143">
-        <f t="shared" si="6"/>
+      <c r="J143">
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G144">
+      <c r="K143" t="str">
+        <f t="shared" si="11"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="144" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H144">
         <v>138</v>
       </c>
-      <c r="H144">
-        <f t="shared" si="5"/>
+      <c r="I144">
+        <f t="shared" si="9"/>
         <v>-0.24298017990326382</v>
       </c>
-      <c r="I144">
-        <f t="shared" si="6"/>
+      <c r="J144">
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G145">
+      <c r="K144" t="str">
+        <f t="shared" si="11"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H145">
         <v>139</v>
       </c>
-      <c r="H145">
-        <f t="shared" si="5"/>
+      <c r="I145">
+        <f t="shared" si="9"/>
         <v>-0.26671275747489825</v>
       </c>
-      <c r="I145">
-        <f t="shared" si="6"/>
+      <c r="J145">
+        <f t="shared" si="10"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G146">
+      <c r="K145" t="str">
+        <f t="shared" si="11"/>
+        <v>5D</v>
+      </c>
+    </row>
+    <row r="146" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H146">
         <v>140</v>
       </c>
-      <c r="H146">
-        <f t="shared" si="5"/>
+      <c r="I146">
+        <f t="shared" si="9"/>
         <v>-0.29028467725446211</v>
       </c>
-      <c r="I146">
-        <f t="shared" si="6"/>
+      <c r="J146">
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G147">
+      <c r="K146" t="str">
+        <f t="shared" si="11"/>
+        <v>5A</v>
+      </c>
+    </row>
+    <row r="147" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H147">
         <v>141</v>
       </c>
-      <c r="H147">
-        <f t="shared" si="5"/>
+      <c r="I147">
+        <f t="shared" si="9"/>
         <v>-0.31368174039889118</v>
       </c>
-      <c r="I147">
-        <f t="shared" si="6"/>
+      <c r="J147">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G148">
+      <c r="K147" t="str">
+        <f t="shared" si="11"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="148" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H148">
         <v>142</v>
       </c>
-      <c r="H148">
-        <f t="shared" si="5"/>
+      <c r="I148">
+        <f t="shared" si="9"/>
         <v>-0.33688985339222011</v>
       </c>
-      <c r="I148">
-        <f t="shared" si="6"/>
+      <c r="J148">
+        <f t="shared" si="10"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G149">
+      <c r="K148" t="str">
+        <f t="shared" si="11"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H149">
         <v>143</v>
       </c>
-      <c r="H149">
-        <f t="shared" si="5"/>
+      <c r="I149">
+        <f t="shared" si="9"/>
         <v>-0.35989503653498811</v>
       </c>
-      <c r="I149">
-        <f t="shared" si="6"/>
+      <c r="J149">
+        <f t="shared" si="10"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G150">
+      <c r="K149" t="str">
+        <f t="shared" si="11"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="150" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H150">
         <v>144</v>
       </c>
-      <c r="H150">
-        <f t="shared" si="5"/>
+      <c r="I150">
+        <f t="shared" si="9"/>
         <v>-0.38268343236508967</v>
       </c>
-      <c r="I150">
-        <f t="shared" si="6"/>
+      <c r="J150">
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
-    </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G151">
+      <c r="K150" t="str">
+        <f t="shared" si="11"/>
+        <v>4F</v>
+      </c>
+    </row>
+    <row r="151" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H151">
         <v>145</v>
       </c>
-      <c r="H151">
-        <f t="shared" si="5"/>
+      <c r="I151">
+        <f t="shared" si="9"/>
         <v>-0.40524131400498969</v>
       </c>
-      <c r="I151">
-        <f t="shared" si="6"/>
+      <c r="J151">
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G152">
+      <c r="K151" t="str">
+        <f t="shared" si="11"/>
+        <v>4C</v>
+      </c>
+    </row>
+    <row r="152" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H152">
         <v>146</v>
       </c>
-      <c r="H152">
-        <f t="shared" si="5"/>
+      <c r="I152">
+        <f t="shared" si="9"/>
         <v>-0.42755509343028181</v>
       </c>
-      <c r="I152">
-        <f t="shared" si="6"/>
+      <c r="J152">
+        <f t="shared" si="10"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G153">
+      <c r="K152" t="str">
+        <f t="shared" si="11"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="153" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H153">
         <v>147</v>
       </c>
-      <c r="H153">
-        <f t="shared" si="5"/>
+      <c r="I153">
+        <f t="shared" si="9"/>
         <v>-0.44961132965460665</v>
       </c>
-      <c r="I153">
-        <f t="shared" si="6"/>
+      <c r="J153">
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G154">
+      <c r="K153" t="str">
+        <f t="shared" si="11"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H154">
         <v>148</v>
       </c>
-      <c r="H154">
-        <f t="shared" si="5"/>
+      <c r="I154">
+        <f t="shared" si="9"/>
         <v>-0.47139673682599764</v>
       </c>
-      <c r="I154">
-        <f t="shared" si="6"/>
+      <c r="J154">
+        <f t="shared" si="10"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G155">
+      <c r="K154" t="str">
+        <f t="shared" si="11"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H155">
         <v>149</v>
       </c>
-      <c r="H155">
-        <f t="shared" si="5"/>
+      <c r="I155">
+        <f t="shared" si="9"/>
         <v>-0.49289819222978393</v>
       </c>
-      <c r="I155">
-        <f t="shared" si="6"/>
+      <c r="J155">
+        <f t="shared" si="10"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G156">
+      <c r="K155" t="str">
+        <f t="shared" si="11"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H156">
         <v>150</v>
       </c>
-      <c r="H156">
-        <f t="shared" si="5"/>
+      <c r="I156">
+        <f t="shared" si="9"/>
         <v>-0.51410274419322155</v>
       </c>
-      <c r="I156">
-        <f t="shared" si="6"/>
+      <c r="J156">
+        <f t="shared" si="10"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G157">
+      <c r="K156" t="str">
+        <f t="shared" si="11"/>
+        <v>3E</v>
+      </c>
+    </row>
+    <row r="157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H157">
         <v>151</v>
       </c>
-      <c r="H157">
-        <f t="shared" si="5"/>
+      <c r="I157">
+        <f t="shared" si="9"/>
         <v>-0.53499761988709693</v>
       </c>
-      <c r="I157">
-        <f t="shared" si="6"/>
+      <c r="J157">
+        <f t="shared" si="10"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G158">
+      <c r="K157" t="str">
+        <f t="shared" si="11"/>
+        <v>3B</v>
+      </c>
+    </row>
+    <row r="158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H158">
         <v>152</v>
       </c>
-      <c r="H158">
-        <f t="shared" si="5"/>
+      <c r="I158">
+        <f t="shared" si="9"/>
         <v>-0.55557023301960196</v>
       </c>
-      <c r="I158">
-        <f t="shared" si="6"/>
+      <c r="J158">
+        <f t="shared" si="10"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G159">
+      <c r="K158" t="str">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H159">
         <v>153</v>
       </c>
-      <c r="H159">
-        <f t="shared" si="5"/>
+      <c r="I159">
+        <f t="shared" si="9"/>
         <v>-0.57580819141784534</v>
       </c>
-      <c r="I159">
-        <f t="shared" si="6"/>
+      <c r="J159">
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G160">
+      <c r="K159" t="str">
+        <f t="shared" si="11"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H160">
         <v>154</v>
       </c>
-      <c r="H160">
-        <f t="shared" si="5"/>
+      <c r="I160">
+        <f t="shared" si="9"/>
         <v>-0.59569930449243325</v>
       </c>
-      <c r="I160">
-        <f t="shared" si="6"/>
+      <c r="J160">
+        <f t="shared" si="10"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G161">
+      <c r="K160" t="str">
+        <f t="shared" si="11"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="161" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H161">
         <v>155</v>
       </c>
-      <c r="H161">
-        <f t="shared" si="5"/>
+      <c r="I161">
+        <f t="shared" si="9"/>
         <v>-0.61523159058062671</v>
       </c>
-      <c r="I161">
-        <f t="shared" si="6"/>
+      <c r="J161">
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G162">
+      <c r="K161" t="str">
+        <f t="shared" si="11"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H162">
         <v>156</v>
       </c>
-      <c r="H162">
-        <f t="shared" si="5"/>
+      <c r="I162">
+        <f t="shared" si="9"/>
         <v>-0.63439328416364527</v>
       </c>
-      <c r="I162">
-        <f t="shared" si="6"/>
+      <c r="J162">
+        <f t="shared" si="10"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G163">
+      <c r="K162" t="str">
+        <f t="shared" si="11"/>
+        <v>2F</v>
+      </c>
+    </row>
+    <row r="163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H163">
         <v>157</v>
       </c>
-      <c r="H163">
-        <f t="shared" si="5"/>
+      <c r="I163">
+        <f t="shared" si="9"/>
         <v>-0.65317284295377653</v>
       </c>
-      <c r="I163">
-        <f t="shared" si="6"/>
+      <c r="J163">
+        <f t="shared" si="10"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G164">
+      <c r="K163" t="str">
+        <f t="shared" si="11"/>
+        <v>2C</v>
+      </c>
+    </row>
+    <row r="164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H164">
         <v>158</v>
       </c>
-      <c r="H164">
-        <f t="shared" si="5"/>
+      <c r="I164">
+        <f t="shared" si="9"/>
         <v>-0.67155895484701844</v>
       </c>
-      <c r="I164">
-        <f t="shared" si="6"/>
+      <c r="J164">
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G165">
+      <c r="K164" t="str">
+        <f t="shared" si="11"/>
+        <v>2A</v>
+      </c>
+    </row>
+    <row r="165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H165">
         <v>159</v>
       </c>
-      <c r="H165">
-        <f t="shared" si="5"/>
+      <c r="I165">
+        <f t="shared" si="9"/>
         <v>-0.68954054473706683</v>
       </c>
-      <c r="I165">
-        <f t="shared" si="6"/>
+      <c r="J165">
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G166">
+      <c r="K165" t="str">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H166">
         <v>160</v>
       </c>
-      <c r="H166">
-        <f t="shared" si="5"/>
+      <c r="I166">
+        <f t="shared" si="9"/>
         <v>-0.70710678118654746</v>
       </c>
-      <c r="I166">
-        <f t="shared" si="6"/>
+      <c r="J166">
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G167">
+      <c r="K166" t="str">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H167">
         <v>161</v>
       </c>
-      <c r="H167">
-        <f t="shared" si="5"/>
+      <c r="I167">
+        <f t="shared" si="9"/>
         <v>-0.72424708295146678</v>
       </c>
-      <c r="I167">
-        <f t="shared" si="6"/>
+      <c r="J167">
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G168">
+      <c r="K167" t="str">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H168">
         <v>162</v>
       </c>
-      <c r="H168">
-        <f t="shared" si="5"/>
+      <c r="I168">
+        <f t="shared" si="9"/>
         <v>-0.74095112535495888</v>
       </c>
-      <c r="I168">
-        <f t="shared" si="6"/>
+      <c r="J168">
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G169">
+      <c r="K168" t="str">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H169">
         <v>163</v>
       </c>
-      <c r="H169">
-        <f t="shared" si="5"/>
+      <c r="I169">
+        <f t="shared" si="9"/>
         <v>-0.75720884650648423</v>
       </c>
-      <c r="I169">
-        <f t="shared" si="6"/>
+      <c r="J169">
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G170">
+      <c r="K169" t="str">
+        <f t="shared" si="11"/>
+        <v>1F</v>
+      </c>
+    </row>
+    <row r="170" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H170">
         <v>164</v>
       </c>
-      <c r="H170">
-        <f t="shared" si="5"/>
+      <c r="I170">
+        <f t="shared" si="9"/>
         <v>-0.77301045336273666</v>
       </c>
-      <c r="I170">
-        <f t="shared" si="6"/>
+      <c r="J170">
+        <f t="shared" si="10"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G171">
+      <c r="K170" t="str">
+        <f t="shared" si="11"/>
+        <v>1D</v>
+      </c>
+    </row>
+    <row r="171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H171">
         <v>165</v>
       </c>
-      <c r="H171">
-        <f t="shared" si="5"/>
+      <c r="I171">
+        <f t="shared" si="9"/>
         <v>-0.78834642762660589</v>
       </c>
-      <c r="I171">
-        <f t="shared" si="6"/>
+      <c r="J171">
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G172">
+      <c r="K171" t="str">
+        <f t="shared" si="11"/>
+        <v>1B</v>
+      </c>
+    </row>
+    <row r="172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H172">
         <v>166</v>
       </c>
-      <c r="H172">
-        <f t="shared" si="5"/>
+      <c r="I172">
+        <f t="shared" si="9"/>
         <v>-0.80320753148064505</v>
       </c>
-      <c r="I172">
-        <f t="shared" si="6"/>
+      <c r="J172">
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G173">
+      <c r="K172" t="str">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H173">
         <v>167</v>
       </c>
-      <c r="H173">
-        <f t="shared" si="5"/>
+      <c r="I173">
+        <f t="shared" si="9"/>
         <v>-0.81758481315158382</v>
       </c>
-      <c r="I173">
-        <f t="shared" si="6"/>
+      <c r="J173">
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G174">
+      <c r="K173" t="str">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H174">
         <v>168</v>
       </c>
-      <c r="H174">
-        <f t="shared" si="5"/>
+      <c r="I174">
+        <f t="shared" si="9"/>
         <v>-0.83146961230254524</v>
       </c>
-      <c r="I174">
-        <f t="shared" si="6"/>
+      <c r="J174">
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G175">
+      <c r="K174" t="str">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H175">
         <v>169</v>
       </c>
-      <c r="H175">
-        <f t="shared" si="5"/>
+      <c r="I175">
+        <f t="shared" si="9"/>
         <v>-0.84485356524970701</v>
       </c>
-      <c r="I175">
-        <f t="shared" si="6"/>
+      <c r="J175">
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G176">
+      <c r="K175" t="str">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H176">
         <v>170</v>
       </c>
-      <c r="H176">
-        <f t="shared" si="5"/>
+      <c r="I176">
+        <f t="shared" si="9"/>
         <v>-0.85772861000027201</v>
       </c>
-      <c r="I176">
-        <f t="shared" si="6"/>
+      <c r="J176">
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G177">
+      <c r="K176" t="str">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H177">
         <v>171</v>
       </c>
-      <c r="H177">
-        <f t="shared" si="5"/>
+      <c r="I177">
+        <f t="shared" si="9"/>
         <v>-0.87008699110871135</v>
       </c>
-      <c r="I177">
-        <f t="shared" si="6"/>
+      <c r="J177">
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G178">
+      <c r="K177" t="str">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H178">
         <v>172</v>
       </c>
-      <c r="H178">
-        <f t="shared" si="5"/>
+      <c r="I178">
+        <f t="shared" si="9"/>
         <v>-0.88192126434835494</v>
       </c>
-      <c r="I178">
-        <f t="shared" si="6"/>
+      <c r="J178">
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G179">
+      <c r="K178" t="str">
+        <f t="shared" si="11"/>
+        <v>0F</v>
+      </c>
+    </row>
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H179">
         <v>173</v>
       </c>
-      <c r="H179">
-        <f t="shared" si="5"/>
+      <c r="I179">
+        <f t="shared" si="9"/>
         <v>-0.89322430119551521</v>
       </c>
-      <c r="I179">
-        <f t="shared" si="6"/>
+      <c r="J179">
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G180">
+      <c r="K179" t="str">
+        <f t="shared" si="11"/>
+        <v>0E</v>
+      </c>
+    </row>
+    <row r="180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H180">
         <v>174</v>
       </c>
-      <c r="H180">
-        <f t="shared" si="5"/>
+      <c r="I180">
+        <f t="shared" si="9"/>
         <v>-0.90398929312344312</v>
       </c>
-      <c r="I180">
-        <f t="shared" si="6"/>
+      <c r="J180">
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G181">
+      <c r="K180" t="str">
+        <f t="shared" si="11"/>
+        <v>0C</v>
+      </c>
+    </row>
+    <row r="181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H181">
         <v>175</v>
       </c>
-      <c r="H181">
-        <f t="shared" si="5"/>
+      <c r="I181">
+        <f t="shared" si="9"/>
         <v>-0.91420975570353047</v>
       </c>
-      <c r="I181">
-        <f t="shared" si="6"/>
+      <c r="J181">
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G182">
+      <c r="K181" t="str">
+        <f t="shared" si="11"/>
+        <v>0B</v>
+      </c>
+    </row>
+    <row r="182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H182">
         <v>176</v>
       </c>
-      <c r="H182">
-        <f t="shared" si="5"/>
+      <c r="I182">
+        <f t="shared" si="9"/>
         <v>-0.92387953251128652</v>
       </c>
-      <c r="I182">
-        <f t="shared" si="6"/>
+      <c r="J182">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G183">
+      <c r="K182" t="str">
+        <f t="shared" si="11"/>
+        <v>0A</v>
+      </c>
+    </row>
+    <row r="183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H183">
         <v>177</v>
       </c>
-      <c r="H183">
-        <f t="shared" si="5"/>
+      <c r="I183">
+        <f t="shared" si="9"/>
         <v>-0.93299279883473896</v>
       </c>
-      <c r="I183">
-        <f t="shared" si="6"/>
+      <c r="J183">
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G184">
+      <c r="K183" t="str">
+        <f t="shared" si="11"/>
+        <v>09</v>
+      </c>
+    </row>
+    <row r="184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H184">
         <v>178</v>
       </c>
-      <c r="H184">
-        <f t="shared" si="5"/>
+      <c r="I184">
+        <f t="shared" si="9"/>
         <v>-0.94154406518302081</v>
       </c>
-      <c r="I184">
-        <f t="shared" si="6"/>
+      <c r="J184">
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G185">
+      <c r="K184" t="str">
+        <f t="shared" si="11"/>
+        <v>07</v>
+      </c>
+    </row>
+    <row r="185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H185">
         <v>179</v>
       </c>
-      <c r="H185">
-        <f t="shared" si="5"/>
+      <c r="I185">
+        <f t="shared" si="9"/>
         <v>-0.94952818059303667</v>
       </c>
-      <c r="I185">
-        <f t="shared" si="6"/>
+      <c r="J185">
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G186">
+      <c r="K185" t="str">
+        <f t="shared" si="11"/>
+        <v>06</v>
+      </c>
+    </row>
+    <row r="186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H186">
         <v>180</v>
       </c>
-      <c r="H186">
-        <f t="shared" si="5"/>
+      <c r="I186">
+        <f t="shared" si="9"/>
         <v>-0.95694033573220882</v>
       </c>
-      <c r="I186">
-        <f t="shared" si="6"/>
+      <c r="J186">
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G187">
+      <c r="K186" t="str">
+        <f t="shared" si="11"/>
+        <v>05</v>
+      </c>
+    </row>
+    <row r="187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H187">
         <v>181</v>
       </c>
-      <c r="H187">
-        <f t="shared" si="5"/>
+      <c r="I187">
+        <f t="shared" si="9"/>
         <v>-0.96377606579543984</v>
       </c>
-      <c r="I187">
-        <f t="shared" si="6"/>
+      <c r="J187">
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G188">
+      <c r="K187" t="str">
+        <f t="shared" si="11"/>
+        <v>05</v>
+      </c>
+    </row>
+    <row r="188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H188">
         <v>182</v>
       </c>
-      <c r="H188">
-        <f t="shared" si="5"/>
+      <c r="I188">
+        <f t="shared" si="9"/>
         <v>-0.97003125319454397</v>
       </c>
-      <c r="I188">
-        <f t="shared" si="6"/>
+      <c r="J188">
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G189">
+      <c r="K188" t="str">
+        <f t="shared" si="11"/>
+        <v>04</v>
+      </c>
+    </row>
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H189">
         <v>183</v>
       </c>
-      <c r="H189">
-        <f t="shared" si="5"/>
+      <c r="I189">
+        <f t="shared" si="9"/>
         <v>-0.97570213003852846</v>
       </c>
-      <c r="I189">
-        <f t="shared" si="6"/>
+      <c r="J189">
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G190">
+      <c r="K189" t="str">
+        <f t="shared" si="11"/>
+        <v>03</v>
+      </c>
+    </row>
+    <row r="190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H190">
         <v>184</v>
       </c>
-      <c r="H190">
-        <f t="shared" si="5"/>
+      <c r="I190">
+        <f t="shared" si="9"/>
         <v>-0.98078528040323032</v>
       </c>
-      <c r="I190">
-        <f t="shared" si="6"/>
+      <c r="J190">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G191">
+      <c r="K190" t="str">
+        <f t="shared" si="11"/>
+        <v>02</v>
+      </c>
+    </row>
+    <row r="191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H191">
         <v>185</v>
       </c>
-      <c r="H191">
-        <f t="shared" si="5"/>
+      <c r="I191">
+        <f t="shared" si="9"/>
         <v>-0.98527764238894111</v>
       </c>
-      <c r="I191">
-        <f t="shared" si="6"/>
+      <c r="J191">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G192">
+      <c r="K191" t="str">
+        <f t="shared" si="11"/>
+        <v>02</v>
+      </c>
+    </row>
+    <row r="192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H192">
         <v>186</v>
       </c>
-      <c r="H192">
-        <f t="shared" si="5"/>
+      <c r="I192">
+        <f t="shared" si="9"/>
         <v>-0.9891765099647809</v>
       </c>
-      <c r="I192">
-        <f t="shared" si="6"/>
+      <c r="J192">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G193">
+      <c r="K192" t="str">
+        <f t="shared" si="11"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="193" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H193">
         <v>187</v>
       </c>
-      <c r="H193">
-        <f t="shared" si="5"/>
+      <c r="I193">
+        <f t="shared" si="9"/>
         <v>-0.99247953459871008</v>
       </c>
-      <c r="I193">
-        <f t="shared" si="6"/>
+      <c r="J193">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G194">
+      <c r="K193" t="str">
+        <f t="shared" si="11"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H194">
         <v>188</v>
       </c>
-      <c r="H194">
-        <f t="shared" si="5"/>
+      <c r="I194">
+        <f t="shared" si="9"/>
         <v>-0.99518472667219693</v>
       </c>
-      <c r="I194">
-        <f t="shared" si="6"/>
+      <c r="J194">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G195">
+      <c r="K194" t="str">
+        <f t="shared" si="11"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H195">
         <v>189</v>
       </c>
-      <c r="H195">
-        <f t="shared" si="5"/>
+      <c r="I195">
+        <f t="shared" si="9"/>
         <v>-0.99729045667869021</v>
       </c>
-      <c r="I195">
-        <f t="shared" si="6"/>
+      <c r="J195">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G196">
+      <c r="K195" t="str">
+        <f t="shared" si="11"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H196">
         <v>190</v>
       </c>
-      <c r="H196">
-        <f t="shared" si="5"/>
+      <c r="I196">
+        <f t="shared" si="9"/>
         <v>-0.99879545620517241</v>
       </c>
-      <c r="I196">
-        <f t="shared" si="6"/>
+      <c r="J196">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G197">
+      <c r="K196" t="str">
+        <f t="shared" si="11"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H197">
         <v>191</v>
       </c>
-      <c r="H197">
-        <f t="shared" si="5"/>
+      <c r="I197">
+        <f t="shared" si="9"/>
         <v>-0.99969881869620425</v>
       </c>
-      <c r="I197">
-        <f t="shared" si="6"/>
+      <c r="J197">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G198">
+      <c r="K197" t="str">
+        <f t="shared" si="11"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H198">
         <v>192</v>
       </c>
-      <c r="H198">
-        <f t="shared" si="5"/>
+      <c r="I198">
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="I198">
-        <f t="shared" si="6"/>
+      <c r="J198">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G199">
+      <c r="K198" t="str">
+        <f t="shared" si="11"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H199">
         <v>193</v>
       </c>
-      <c r="H199">
-        <f t="shared" ref="H199:H261" si="7">SIN(G199 * 2 * PI()/256)</f>
+      <c r="I199">
+        <f t="shared" ref="I199:I261" si="12">SIN(H199 * 2 * PI()/256)</f>
         <v>-0.99969881869620425</v>
       </c>
-      <c r="I199">
-        <f t="shared" ref="I199:I261" si="8">ROUND((H199 + 1) * 127.5, 0)</f>
+      <c r="J199">
+        <f t="shared" ref="J199:J261" si="13">ROUND((I199 + 1) * 127.5, 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G200">
+      <c r="K199" t="str">
+        <f t="shared" ref="K199:K261" si="14">DEC2HEX(J199, 2)</f>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="200" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H200">
         <v>194</v>
       </c>
-      <c r="H200">
-        <f t="shared" si="7"/>
+      <c r="I200">
+        <f t="shared" si="12"/>
         <v>-0.99879545620517241</v>
       </c>
-      <c r="I200">
-        <f t="shared" si="8"/>
+      <c r="J200">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G201">
+      <c r="K200" t="str">
+        <f t="shared" si="14"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H201">
         <v>195</v>
       </c>
-      <c r="H201">
-        <f t="shared" si="7"/>
+      <c r="I201">
+        <f t="shared" si="12"/>
         <v>-0.99729045667869021</v>
       </c>
-      <c r="I201">
-        <f t="shared" si="8"/>
+      <c r="J201">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G202">
+      <c r="K201" t="str">
+        <f t="shared" si="14"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H202">
         <v>196</v>
       </c>
-      <c r="H202">
-        <f t="shared" si="7"/>
+      <c r="I202">
+        <f t="shared" si="12"/>
         <v>-0.99518472667219693</v>
       </c>
-      <c r="I202">
-        <f t="shared" si="8"/>
+      <c r="J202">
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G203">
+      <c r="K202" t="str">
+        <f t="shared" si="14"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H203">
         <v>197</v>
       </c>
-      <c r="H203">
-        <f t="shared" si="7"/>
+      <c r="I203">
+        <f t="shared" si="12"/>
         <v>-0.99247953459871008</v>
       </c>
-      <c r="I203">
-        <f t="shared" si="8"/>
+      <c r="J203">
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G204">
+      <c r="K203" t="str">
+        <f t="shared" si="14"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H204">
         <v>198</v>
       </c>
-      <c r="H204">
-        <f t="shared" si="7"/>
+      <c r="I204">
+        <f t="shared" si="12"/>
         <v>-0.9891765099647809</v>
       </c>
-      <c r="I204">
-        <f t="shared" si="8"/>
+      <c r="J204">
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G205">
+      <c r="K204" t="str">
+        <f t="shared" si="14"/>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H205">
         <v>199</v>
       </c>
-      <c r="H205">
-        <f t="shared" si="7"/>
+      <c r="I205">
+        <f t="shared" si="12"/>
         <v>-0.98527764238894122</v>
       </c>
-      <c r="I205">
-        <f t="shared" si="8"/>
+      <c r="J205">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G206">
+      <c r="K205" t="str">
+        <f t="shared" si="14"/>
+        <v>02</v>
+      </c>
+    </row>
+    <row r="206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H206">
         <v>200</v>
       </c>
-      <c r="H206">
-        <f t="shared" si="7"/>
+      <c r="I206">
+        <f t="shared" si="12"/>
         <v>-0.98078528040323043</v>
       </c>
-      <c r="I206">
-        <f t="shared" si="8"/>
+      <c r="J206">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G207">
+      <c r="K206" t="str">
+        <f t="shared" si="14"/>
+        <v>02</v>
+      </c>
+    </row>
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H207">
         <v>201</v>
       </c>
-      <c r="H207">
-        <f t="shared" si="7"/>
+      <c r="I207">
+        <f t="shared" si="12"/>
         <v>-0.97570213003852857</v>
       </c>
-      <c r="I207">
-        <f t="shared" si="8"/>
+      <c r="J207">
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G208">
+      <c r="K207" t="str">
+        <f t="shared" si="14"/>
+        <v>03</v>
+      </c>
+    </row>
+    <row r="208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H208">
         <v>202</v>
       </c>
-      <c r="H208">
-        <f t="shared" si="7"/>
+      <c r="I208">
+        <f t="shared" si="12"/>
         <v>-0.97003125319454397</v>
       </c>
-      <c r="I208">
-        <f t="shared" si="8"/>
+      <c r="J208">
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G209">
+      <c r="K208" t="str">
+        <f t="shared" si="14"/>
+        <v>04</v>
+      </c>
+    </row>
+    <row r="209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H209">
         <v>203</v>
       </c>
-      <c r="H209">
-        <f t="shared" si="7"/>
+      <c r="I209">
+        <f t="shared" si="12"/>
         <v>-0.96377606579543995</v>
       </c>
-      <c r="I209">
-        <f t="shared" si="8"/>
+      <c r="J209">
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G210">
+      <c r="K209" t="str">
+        <f t="shared" si="14"/>
+        <v>05</v>
+      </c>
+    </row>
+    <row r="210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H210">
         <v>204</v>
       </c>
-      <c r="H210">
-        <f t="shared" si="7"/>
+      <c r="I210">
+        <f t="shared" si="12"/>
         <v>-0.95694033573220894</v>
       </c>
-      <c r="I210">
-        <f t="shared" si="8"/>
+      <c r="J210">
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G211">
+      <c r="K210" t="str">
+        <f t="shared" si="14"/>
+        <v>05</v>
+      </c>
+    </row>
+    <row r="211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H211">
         <v>205</v>
       </c>
-      <c r="H211">
-        <f t="shared" si="7"/>
+      <c r="I211">
+        <f t="shared" si="12"/>
         <v>-0.94952818059303679</v>
       </c>
-      <c r="I211">
-        <f t="shared" si="8"/>
+      <c r="J211">
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G212">
+      <c r="K211" t="str">
+        <f t="shared" si="14"/>
+        <v>06</v>
+      </c>
+    </row>
+    <row r="212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H212">
         <v>206</v>
       </c>
-      <c r="H212">
-        <f t="shared" si="7"/>
+      <c r="I212">
+        <f t="shared" si="12"/>
         <v>-0.94154406518302092</v>
       </c>
-      <c r="I212">
-        <f t="shared" si="8"/>
+      <c r="J212">
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G213">
+      <c r="K212" t="str">
+        <f t="shared" si="14"/>
+        <v>07</v>
+      </c>
+    </row>
+    <row r="213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H213">
         <v>207</v>
       </c>
-      <c r="H213">
-        <f t="shared" si="7"/>
+      <c r="I213">
+        <f t="shared" si="12"/>
         <v>-0.93299279883473907</v>
       </c>
-      <c r="I213">
-        <f t="shared" si="8"/>
+      <c r="J213">
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G214">
+      <c r="K213" t="str">
+        <f t="shared" si="14"/>
+        <v>09</v>
+      </c>
+    </row>
+    <row r="214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H214">
         <v>208</v>
       </c>
-      <c r="H214">
-        <f t="shared" si="7"/>
+      <c r="I214">
+        <f t="shared" si="12"/>
         <v>-0.92387953251128663</v>
       </c>
-      <c r="I214">
-        <f t="shared" si="8"/>
+      <c r="J214">
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G215">
+      <c r="K214" t="str">
+        <f t="shared" si="14"/>
+        <v>0A</v>
+      </c>
+    </row>
+    <row r="215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H215">
         <v>209</v>
       </c>
-      <c r="H215">
-        <f t="shared" si="7"/>
+      <c r="I215">
+        <f t="shared" si="12"/>
         <v>-0.91420975570353058</v>
       </c>
-      <c r="I215">
-        <f t="shared" si="8"/>
+      <c r="J215">
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G216">
+      <c r="K215" t="str">
+        <f t="shared" si="14"/>
+        <v>0B</v>
+      </c>
+    </row>
+    <row r="216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H216">
         <v>210</v>
       </c>
-      <c r="H216">
-        <f t="shared" si="7"/>
+      <c r="I216">
+        <f t="shared" si="12"/>
         <v>-0.90398929312344334</v>
       </c>
-      <c r="I216">
-        <f t="shared" si="8"/>
+      <c r="J216">
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G217">
+      <c r="K216" t="str">
+        <f t="shared" si="14"/>
+        <v>0C</v>
+      </c>
+    </row>
+    <row r="217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H217">
         <v>211</v>
       </c>
-      <c r="H217">
-        <f t="shared" si="7"/>
+      <c r="I217">
+        <f t="shared" si="12"/>
         <v>-0.89322430119551532</v>
       </c>
-      <c r="I217">
-        <f t="shared" si="8"/>
+      <c r="J217">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G218">
+      <c r="K217" t="str">
+        <f t="shared" si="14"/>
+        <v>0E</v>
+      </c>
+    </row>
+    <row r="218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H218">
         <v>212</v>
       </c>
-      <c r="H218">
-        <f t="shared" si="7"/>
+      <c r="I218">
+        <f t="shared" si="12"/>
         <v>-0.88192126434835505</v>
       </c>
-      <c r="I218">
-        <f t="shared" si="8"/>
+      <c r="J218">
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G219">
+      <c r="K218" t="str">
+        <f t="shared" si="14"/>
+        <v>0F</v>
+      </c>
+    </row>
+    <row r="219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H219">
         <v>213</v>
       </c>
-      <c r="H219">
-        <f t="shared" si="7"/>
+      <c r="I219">
+        <f t="shared" si="12"/>
         <v>-0.87008699110871146</v>
       </c>
-      <c r="I219">
-        <f t="shared" si="8"/>
+      <c r="J219">
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G220">
+      <c r="K219" t="str">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H220">
         <v>214</v>
       </c>
-      <c r="H220">
-        <f t="shared" si="7"/>
+      <c r="I220">
+        <f t="shared" si="12"/>
         <v>-0.85772861000027223</v>
       </c>
-      <c r="I220">
-        <f t="shared" si="8"/>
+      <c r="J220">
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G221">
+      <c r="K220" t="str">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H221">
         <v>215</v>
       </c>
-      <c r="H221">
-        <f t="shared" si="7"/>
+      <c r="I221">
+        <f t="shared" si="12"/>
         <v>-0.84485356524970723</v>
       </c>
-      <c r="I221">
-        <f t="shared" si="8"/>
+      <c r="J221">
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G222">
+      <c r="K221" t="str">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H222">
         <v>216</v>
       </c>
-      <c r="H222">
-        <f t="shared" si="7"/>
+      <c r="I222">
+        <f t="shared" si="12"/>
         <v>-0.83146961230254546</v>
       </c>
-      <c r="I222">
-        <f t="shared" si="8"/>
+      <c r="J222">
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G223">
+      <c r="K222" t="str">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H223">
         <v>217</v>
       </c>
-      <c r="H223">
-        <f t="shared" si="7"/>
+      <c r="I223">
+        <f t="shared" si="12"/>
         <v>-0.81758481315158404</v>
       </c>
-      <c r="I223">
-        <f t="shared" si="8"/>
+      <c r="J223">
+        <f t="shared" si="13"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G224">
+      <c r="K223" t="str">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H224">
         <v>218</v>
       </c>
-      <c r="H224">
-        <f t="shared" si="7"/>
+      <c r="I224">
+        <f t="shared" si="12"/>
         <v>-0.80320753148064528</v>
       </c>
-      <c r="I224">
-        <f t="shared" si="8"/>
+      <c r="J224">
+        <f t="shared" si="13"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G225">
+      <c r="K224" t="str">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H225">
         <v>219</v>
       </c>
-      <c r="H225">
-        <f t="shared" si="7"/>
+      <c r="I225">
+        <f t="shared" si="12"/>
         <v>-0.78834642762660612</v>
       </c>
-      <c r="I225">
-        <f t="shared" si="8"/>
+      <c r="J225">
+        <f t="shared" si="13"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G226">
+      <c r="K225" t="str">
+        <f t="shared" si="14"/>
+        <v>1B</v>
+      </c>
+    </row>
+    <row r="226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H226">
         <v>220</v>
       </c>
-      <c r="H226">
-        <f t="shared" si="7"/>
+      <c r="I226">
+        <f t="shared" si="12"/>
         <v>-0.77301045336273688</v>
       </c>
-      <c r="I226">
-        <f t="shared" si="8"/>
+      <c r="J226">
+        <f t="shared" si="13"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G227">
+      <c r="K226" t="str">
+        <f t="shared" si="14"/>
+        <v>1D</v>
+      </c>
+    </row>
+    <row r="227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H227">
         <v>221</v>
       </c>
-      <c r="H227">
-        <f t="shared" si="7"/>
+      <c r="I227">
+        <f t="shared" si="12"/>
         <v>-0.75720884650648457</v>
       </c>
-      <c r="I227">
-        <f t="shared" si="8"/>
+      <c r="J227">
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G228">
+      <c r="K227" t="str">
+        <f t="shared" si="14"/>
+        <v>1F</v>
+      </c>
+    </row>
+    <row r="228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H228">
         <v>222</v>
       </c>
-      <c r="H228">
-        <f t="shared" si="7"/>
+      <c r="I228">
+        <f t="shared" si="12"/>
         <v>-0.74095112535495911</v>
       </c>
-      <c r="I228">
-        <f t="shared" si="8"/>
+      <c r="J228">
+        <f t="shared" si="13"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G229">
+      <c r="K228" t="str">
+        <f t="shared" si="14"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H229">
         <v>223</v>
       </c>
-      <c r="H229">
-        <f t="shared" si="7"/>
+      <c r="I229">
+        <f t="shared" si="12"/>
         <v>-0.724247082951467</v>
       </c>
-      <c r="I229">
-        <f t="shared" si="8"/>
+      <c r="J229">
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G230">
+      <c r="K229" t="str">
+        <f t="shared" si="14"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H230">
         <v>224</v>
       </c>
-      <c r="H230">
-        <f t="shared" si="7"/>
+      <c r="I230">
+        <f t="shared" si="12"/>
         <v>-0.70710678118654768</v>
       </c>
-      <c r="I230">
-        <f t="shared" si="8"/>
+      <c r="J230">
+        <f t="shared" si="13"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G231">
+      <c r="K230" t="str">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H231">
         <v>225</v>
       </c>
-      <c r="H231">
-        <f t="shared" si="7"/>
+      <c r="I231">
+        <f t="shared" si="12"/>
         <v>-0.68954054473706716</v>
       </c>
-      <c r="I231">
-        <f t="shared" si="8"/>
+      <c r="J231">
+        <f t="shared" si="13"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G232">
+      <c r="K231" t="str">
+        <f t="shared" si="14"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H232">
         <v>226</v>
       </c>
-      <c r="H232">
-        <f t="shared" si="7"/>
+      <c r="I232">
+        <f t="shared" si="12"/>
         <v>-0.67155895484701866</v>
       </c>
-      <c r="I232">
-        <f t="shared" si="8"/>
+      <c r="J232">
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G233">
+      <c r="K232" t="str">
+        <f t="shared" si="14"/>
+        <v>2A</v>
+      </c>
+    </row>
+    <row r="233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H233">
         <v>227</v>
       </c>
-      <c r="H233">
-        <f t="shared" si="7"/>
+      <c r="I233">
+        <f t="shared" si="12"/>
         <v>-0.65317284295377709</v>
       </c>
-      <c r="I233">
-        <f t="shared" si="8"/>
+      <c r="J233">
+        <f t="shared" si="13"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G234">
+      <c r="K233" t="str">
+        <f t="shared" si="14"/>
+        <v>2C</v>
+      </c>
+    </row>
+    <row r="234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H234">
         <v>228</v>
       </c>
-      <c r="H234">
-        <f t="shared" si="7"/>
+      <c r="I234">
+        <f t="shared" si="12"/>
         <v>-0.63439328416364593</v>
       </c>
-      <c r="I234">
-        <f t="shared" si="8"/>
+      <c r="J234">
+        <f t="shared" si="13"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G235">
+      <c r="K234" t="str">
+        <f t="shared" si="14"/>
+        <v>2F</v>
+      </c>
+    </row>
+    <row r="235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H235">
         <v>229</v>
       </c>
-      <c r="H235">
-        <f t="shared" si="7"/>
+      <c r="I235">
+        <f t="shared" si="12"/>
         <v>-0.61523159058062737</v>
       </c>
-      <c r="I235">
-        <f t="shared" si="8"/>
+      <c r="J235">
+        <f t="shared" si="13"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G236">
+      <c r="K235" t="str">
+        <f t="shared" si="14"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H236">
         <v>230</v>
       </c>
-      <c r="H236">
-        <f t="shared" si="7"/>
+      <c r="I236">
+        <f t="shared" si="12"/>
         <v>-0.59569930449243325</v>
       </c>
-      <c r="I236">
-        <f t="shared" si="8"/>
+      <c r="J236">
+        <f t="shared" si="13"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G237">
+      <c r="K236" t="str">
+        <f t="shared" si="14"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H237">
         <v>231</v>
       </c>
-      <c r="H237">
-        <f t="shared" si="7"/>
+      <c r="I237">
+        <f t="shared" si="12"/>
         <v>-0.57580819141784523</v>
       </c>
-      <c r="I237">
-        <f t="shared" si="8"/>
+      <c r="J237">
+        <f t="shared" si="13"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G238">
+      <c r="K237" t="str">
+        <f t="shared" si="14"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H238">
         <v>232</v>
       </c>
-      <c r="H238">
-        <f t="shared" si="7"/>
+      <c r="I238">
+        <f t="shared" si="12"/>
         <v>-0.55557023301960218</v>
       </c>
-      <c r="I238">
-        <f t="shared" si="8"/>
+      <c r="J238">
+        <f t="shared" si="13"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G239">
+      <c r="K238" t="str">
+        <f t="shared" si="14"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H239">
         <v>233</v>
       </c>
-      <c r="H239">
-        <f t="shared" si="7"/>
+      <c r="I239">
+        <f t="shared" si="12"/>
         <v>-0.53499761988709726</v>
       </c>
-      <c r="I239">
-        <f t="shared" si="8"/>
+      <c r="J239">
+        <f t="shared" si="13"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G240">
+      <c r="K239" t="str">
+        <f t="shared" si="14"/>
+        <v>3B</v>
+      </c>
+    </row>
+    <row r="240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H240">
         <v>234</v>
       </c>
-      <c r="H240">
-        <f t="shared" si="7"/>
+      <c r="I240">
+        <f t="shared" si="12"/>
         <v>-0.51410274419322188</v>
       </c>
-      <c r="I240">
-        <f t="shared" si="8"/>
+      <c r="J240">
+        <f t="shared" si="13"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G241">
+      <c r="K240" t="str">
+        <f t="shared" si="14"/>
+        <v>3E</v>
+      </c>
+    </row>
+    <row r="241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H241">
         <v>235</v>
       </c>
-      <c r="H241">
-        <f t="shared" si="7"/>
+      <c r="I241">
+        <f t="shared" si="12"/>
         <v>-0.49289819222978426</v>
       </c>
-      <c r="I241">
-        <f t="shared" si="8"/>
+      <c r="J241">
+        <f t="shared" si="13"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G242">
+      <c r="K241" t="str">
+        <f t="shared" si="14"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H242">
         <v>236</v>
       </c>
-      <c r="H242">
-        <f t="shared" si="7"/>
+      <c r="I242">
+        <f t="shared" si="12"/>
         <v>-0.47139673682599792</v>
       </c>
-      <c r="I242">
-        <f t="shared" si="8"/>
+      <c r="J242">
+        <f t="shared" si="13"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G243">
+      <c r="K242" t="str">
+        <f t="shared" si="14"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H243">
         <v>237</v>
       </c>
-      <c r="H243">
-        <f t="shared" si="7"/>
+      <c r="I243">
+        <f t="shared" si="12"/>
         <v>-0.44961132965460698</v>
       </c>
-      <c r="I243">
-        <f t="shared" si="8"/>
+      <c r="J243">
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G244">
+      <c r="K243" t="str">
+        <f t="shared" si="14"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H244">
         <v>238</v>
       </c>
-      <c r="H244">
-        <f t="shared" si="7"/>
+      <c r="I244">
+        <f t="shared" si="12"/>
         <v>-0.42755509343028253</v>
       </c>
-      <c r="I244">
-        <f t="shared" si="8"/>
+      <c r="J244">
+        <f t="shared" si="13"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G245">
+      <c r="K244" t="str">
+        <f t="shared" si="14"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H245">
         <v>239</v>
       </c>
-      <c r="H245">
-        <f t="shared" si="7"/>
+      <c r="I245">
+        <f t="shared" si="12"/>
         <v>-0.40524131400499042</v>
       </c>
-      <c r="I245">
-        <f t="shared" si="8"/>
+      <c r="J245">
+        <f t="shared" si="13"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G246">
+      <c r="K245" t="str">
+        <f t="shared" si="14"/>
+        <v>4C</v>
+      </c>
+    </row>
+    <row r="246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H246">
         <v>240</v>
       </c>
-      <c r="H246">
-        <f t="shared" si="7"/>
+      <c r="I246">
+        <f t="shared" si="12"/>
         <v>-0.38268343236509039</v>
       </c>
-      <c r="I246">
-        <f t="shared" si="8"/>
+      <c r="J246">
+        <f t="shared" si="13"/>
         <v>79</v>
       </c>
-    </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G247">
+      <c r="K246" t="str">
+        <f t="shared" si="14"/>
+        <v>4F</v>
+      </c>
+    </row>
+    <row r="247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H247">
         <v>241</v>
       </c>
-      <c r="H247">
-        <f t="shared" si="7"/>
+      <c r="I247">
+        <f t="shared" si="12"/>
         <v>-0.359895036534988</v>
       </c>
-      <c r="I247">
-        <f t="shared" si="8"/>
+      <c r="J247">
+        <f t="shared" si="13"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G248">
+      <c r="K247" t="str">
+        <f t="shared" si="14"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H248">
         <v>242</v>
       </c>
-      <c r="H248">
-        <f t="shared" si="7"/>
+      <c r="I248">
+        <f t="shared" si="12"/>
         <v>-0.33688985339222</v>
       </c>
-      <c r="I248">
-        <f t="shared" si="8"/>
+      <c r="J248">
+        <f t="shared" si="13"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G249">
+      <c r="K248" t="str">
+        <f t="shared" si="14"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H249">
         <v>243</v>
       </c>
-      <c r="H249">
-        <f t="shared" si="7"/>
+      <c r="I249">
+        <f t="shared" si="12"/>
         <v>-0.31368174039889152</v>
       </c>
-      <c r="I249">
-        <f t="shared" si="8"/>
+      <c r="J249">
+        <f t="shared" si="13"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G250">
+      <c r="K249" t="str">
+        <f t="shared" si="14"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="250" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H250">
         <v>244</v>
       </c>
-      <c r="H250">
-        <f t="shared" si="7"/>
+      <c r="I250">
+        <f t="shared" si="12"/>
         <v>-0.2902846772544625</v>
       </c>
-      <c r="I250">
-        <f t="shared" si="8"/>
+      <c r="J250">
+        <f t="shared" si="13"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G251">
+      <c r="K250" t="str">
+        <f t="shared" si="14"/>
+        <v>5A</v>
+      </c>
+    </row>
+    <row r="251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H251">
         <v>245</v>
       </c>
-      <c r="H251">
-        <f t="shared" si="7"/>
+      <c r="I251">
+        <f t="shared" si="12"/>
         <v>-0.26671275747489859</v>
       </c>
-      <c r="I251">
-        <f t="shared" si="8"/>
+      <c r="J251">
+        <f t="shared" si="13"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G252">
+      <c r="K251" t="str">
+        <f t="shared" si="14"/>
+        <v>5D</v>
+      </c>
+    </row>
+    <row r="252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H252">
         <v>246</v>
       </c>
-      <c r="H252">
-        <f t="shared" si="7"/>
+      <c r="I252">
+        <f t="shared" si="12"/>
         <v>-0.24298017990326418</v>
       </c>
-      <c r="I252">
-        <f t="shared" si="8"/>
+      <c r="J252">
+        <f t="shared" si="13"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G253">
+      <c r="K252" t="str">
+        <f t="shared" si="14"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H253">
         <v>247</v>
       </c>
-      <c r="H253">
-        <f t="shared" si="7"/>
+      <c r="I253">
+        <f t="shared" si="12"/>
         <v>-0.21910124015687016</v>
       </c>
-      <c r="I253">
-        <f t="shared" si="8"/>
+      <c r="J253">
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G254">
+      <c r="K253" t="str">
+        <f t="shared" si="14"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H254">
         <v>248</v>
       </c>
-      <c r="H254">
-        <f t="shared" si="7"/>
+      <c r="I254">
+        <f t="shared" si="12"/>
         <v>-0.19509032201612872</v>
       </c>
-      <c r="I254">
-        <f t="shared" si="8"/>
+      <c r="J254">
+        <f t="shared" si="13"/>
         <v>103</v>
       </c>
-    </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G255">
+      <c r="K254" t="str">
+        <f t="shared" si="14"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H255">
         <v>249</v>
       </c>
-      <c r="H255">
-        <f t="shared" si="7"/>
+      <c r="I255">
+        <f t="shared" si="12"/>
         <v>-0.17096188876030177</v>
       </c>
-      <c r="I255">
-        <f t="shared" si="8"/>
+      <c r="J255">
+        <f t="shared" si="13"/>
         <v>106</v>
       </c>
-    </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G256">
+      <c r="K255" t="str">
+        <f t="shared" si="14"/>
+        <v>6A</v>
+      </c>
+    </row>
+    <row r="256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H256">
         <v>250</v>
       </c>
-      <c r="H256">
-        <f t="shared" si="7"/>
+      <c r="I256">
+        <f t="shared" si="12"/>
         <v>-0.14673047445536239</v>
       </c>
-      <c r="I256">
-        <f t="shared" si="8"/>
+      <c r="J256">
+        <f t="shared" si="13"/>
         <v>109</v>
       </c>
-    </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G257">
+      <c r="K256" t="str">
+        <f t="shared" si="14"/>
+        <v>6D</v>
+      </c>
+    </row>
+    <row r="257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H257">
         <v>251</v>
       </c>
-      <c r="H257">
-        <f t="shared" si="7"/>
+      <c r="I257">
+        <f t="shared" si="12"/>
         <v>-0.12241067519921603</v>
       </c>
-      <c r="I257">
-        <f t="shared" si="8"/>
+      <c r="J257">
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
-    </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G258">
+      <c r="K257" t="str">
+        <f t="shared" si="14"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H258">
         <v>252</v>
       </c>
-      <c r="H258">
-        <f t="shared" si="7"/>
+      <c r="I258">
+        <f t="shared" si="12"/>
         <v>-9.8017140329560506E-2</v>
       </c>
-      <c r="I258">
-        <f t="shared" si="8"/>
+      <c r="J258">
+        <f t="shared" si="13"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G259">
+      <c r="K258" t="str">
+        <f t="shared" si="14"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H259">
         <v>253</v>
       </c>
-      <c r="H259">
-        <f t="shared" si="7"/>
+      <c r="I259">
+        <f t="shared" si="12"/>
         <v>-7.3564563599667412E-2</v>
       </c>
-      <c r="I259">
-        <f t="shared" si="8"/>
+      <c r="J259">
+        <f t="shared" si="13"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G260">
+      <c r="K259" t="str">
+        <f t="shared" si="14"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H260">
         <v>254</v>
       </c>
-      <c r="H260">
-        <f t="shared" si="7"/>
+      <c r="I260">
+        <f t="shared" si="12"/>
         <v>-4.9067674327418091E-2</v>
       </c>
-      <c r="I260">
-        <f t="shared" si="8"/>
+      <c r="J260">
+        <f t="shared" si="13"/>
         <v>121</v>
       </c>
-    </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G261">
+      <c r="K260" t="str">
+        <f t="shared" si="14"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H261">
         <v>255</v>
       </c>
-      <c r="H261">
-        <f t="shared" si="7"/>
+      <c r="I261">
+        <f t="shared" si="12"/>
         <v>-2.4541228522912448E-2</v>
       </c>
-      <c r="I261">
-        <f t="shared" si="8"/>
+      <c r="J261">
+        <f t="shared" si="13"/>
         <v>124</v>
+      </c>
+      <c r="K261" t="str">
+        <f t="shared" si="14"/>
+        <v>7C</v>
       </c>
     </row>
   </sheetData>
